--- a/results/Int Task Remove ACC -1.0/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC -1.0/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0017114914425427562 +/- 0.0011852517988793167</t>
+          <t>0.0007946210268949039 +/- 0.0016638945707599252</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.16870415647475e-05 +/- 0.0007616097673824538</t>
+          <t>0.0004889975550122605 +/- 0.001042709175380925</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-5.551115123125783e-17 +/- 0.0014657186807190482</t>
+          <t>0.001039119804401012 +/- 0.0015655560482720804</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.0010696821515892019 +/- 0.0011455785338625472</t>
+          <t>0.003636919315403453 +/- 0.0011390369898278913</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.002414425427872824 +/- 0.0012781493683573912</t>
+          <t>-0.00042787286063566965 +/- 0.0016067774361974154</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.004125916870415658 +/- 0.0016070680715323834</t>
+          <t>0.0011919315403423393 +/- 0.0013630258631404592</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.00024449877750606366 +/- 0.00018337408312956162</t>
+          <t>0.0002139364303178737 +/- 0.0003629077654962743</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.003117359413202936 +/- 0.0013516714173286183</t>
+          <t>0.003056234718826445 +/- 0.0008535599048758416</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.014975550122249371 +/- 0.0020456235367581335</t>
+          <t>0.0246943765281174 +/- 0.0034733673949084052</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.017634474327628324 +/- 0.002857375161034869</t>
+          <t>0.015647921760391238 +/- 0.0024365686342291957</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-0.002536674816625939 +/- 0.000736673031368839</t>
+          <t>0.005134474327628402 +/- 0.001716940330707619</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.002995110024449843 +/- 0.0008836694556724349</t>
+          <t>0.008649144254278762 +/- 0.00167424766806875</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.005287286063569663 +/- 0.0023871912695817457</t>
+          <t>0.004095354523227434 +/- 0.0017460705204261377</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.008251833740831282 +/- 0.0020728392368964763</t>
+          <t>0.0077322738386308544 +/- 0.0029092079801741593</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.012286063569682138 +/- 0.002021740269992823</t>
+          <t>0.01638141809290956 +/- 0.001361311580154064</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.0008557457212714281 +/- 0.0017114914425427688</t>
+          <t>0.00446210268948658 +/- 0.0017353385778213265</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.002842298288508549 +/- 0.0010938588122355367</t>
+          <t>0.0009779951100244877 +/- 0.001917406740997326</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-0.003514669926650382 +/- 0.0014862856254019188</t>
+          <t>-0.0007640586797065696 +/- 0.0015357389396578125</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.0018948655256723402 +/- 0.0007707530692493198</t>
+          <t>0.008282396088019617 +/- 0.0013283199151650602</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00015281173594128283 +/- 0.00015281173594128283</t>
+          <t>0.00018337408312960602 +/- 0.0002027276766721144</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.015158924205378944 +/- 0.0012980905000975099</t>
+          <t>0.016442542787286085 +/- 0.001592764574669366</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-0.0033618581907090663 +/- 0.0014269703581819963</t>
+          <t>-9.16870415647475e-05 +/- 0.0011601621574634643</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.0014669926650366372 +/- 0.0010917219498466925</t>
+          <t>-0.0030256723716380884 +/- 0.0011225163613818288</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.002933985330073374 +/- 0.0008336296880798184</t>
+          <t>-0.0007029339853300232 +/- 0.0005643699667671004</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0018031784841076258 +/- 0.001026913057237874</t>
+          <t>0.001375305623471912 +/- 0.0018451661183525206</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-3.3306690738754695e-17 +/- 0.0006969287439481425</t>
+          <t>-0.0016198044009779534 +/- 0.00045434195438015355</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.00033618581907087777 +/- 0.0017791906574361736</t>
+          <t>0.002628361858190731 +/- 0.0015293393646939946</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-0.0040036674816626315 +/- 0.001314180929095352</t>
+          <t>0.0010085574572127442 +/- 0.0008319472853799572</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>-0.003361858190709077 +/- 0.0013391749572253563</t>
+          <t>0.0003667481662592009 +/- 0.0011002444987775132</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.0054706601466993025 +/- 0.001026913057237844</t>
+          <t>-0.006143031784841035 +/- 0.0012998881612553141</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-0.0003056234718826878 +/- 0.0005635418372428358</t>
+          <t>-0.0006723716381417777 +/- 0.00044917293571819446</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.00033618581907094434 +/- 0.00042016280821723177</t>
+          <t>-0.0008557457212713393 +/- 0.0004695076863000435</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,122 +1046,122 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.010452322738386343 +/- 0.001722371980880848</t>
+          <t>-0.005012224938875254 +/- 0.001033712379296303</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.00012224938875309287 +/- 0.001434803740135135</t>
+          <t>0.005837408312958492 +/- 0.0007160986866662607</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>-0.0009474327628362311 +/- 0.0005543507685579741</t>
+          <t>-0.0007640586797065696 +/- 0.00041569286395890323</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-4.4408920985006264e-17 +/- 0.0007232371372982426</t>
+          <t>0.0013447432762836442 +/- 0.0008665921075035305</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.0025061124694376823 +/- 0.000983708859378433</t>
+          <t>-0.0004889975550121828 +/- 0.0020050390546279503</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>-0.008465770171149167 +/- 0.0009173796466872818</t>
+          <t>-0.003331295843520743 +/- 0.001747407378841402</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.0010391198044009454 +/- 0.0005668470963016921</t>
+          <t>-0.0010696821515892019 +/- 0.0007881293984246808</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.0002444987775060747 +/- 0.0014387044371564426</t>
+          <t>0.00027506112469439793 +/- 0.0012182843171145866</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.004156479217603937 +/- 0.0006583331060066801</t>
+          <t>-0.002139364303178437 +/- 0.0006410812030379704</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0013447432762835776 +/- 0.001312402845573606</t>
+          <t>-0.0036063569682151186 +/- 0.001425660609986641</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.0038508557457212376 +/- 0.0013544327509878013</t>
+          <t>-0.003973105134474275 +/- 0.0019037177875791365</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.00042787286063566965 +/- 0.0017191150501742294</t>
+          <t>0.0022310513447433068 +/- 0.001367131372025999</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-0.00094743276283622 +/- 0.0005870835181020204</t>
+          <t>-0.0018337408312958047 +/- 0.001049851102525515</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.0001833740831296171 +/- 0.0011036350907865206</t>
+          <t>-0.001069682151589213 +/- 0.001347865346650359</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.00012224938875302627 +/- 0.0005328727314842058</t>
+          <t>0.00042787286063571405 +/- 0.0006861229926846912</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.002750611246943746 +/- 0.0015821734847854326</t>
+          <t>-0.0004889975550121828 +/- 0.0008109107066883547</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.0013753056234718452 +/- 0.0015478554110147506</t>
+          <t>0.0006723716381418443 +/- 0.0016672593761596513</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-0.0003973105134474575 +/- 0.0015883602029567571</t>
+          <t>-0.0013447432762835776 +/- 0.0014859713668879174</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-0.0018337408312958602 +/- 0.0016172074028512062</t>
+          <t>-0.0001833740831295394 +/- 0.001929062816388687</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-0.0013447432762836442 +/- 0.00039138901206803235</t>
+          <t>-0.0008863080684596402 +/- 0.0006476045262963527</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.0009779951100243878 +/- 0.0006233520187766116</t>
+          <t>-0.0004584352078239151 +/- 0.0007640586797065918</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>-2.2204460492503132e-17 +/- 0.00019329325551150237</t>
+          <t>-0.00030562347188261007 +/- 0.0003616185686491166</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.0017114914425427562 +/- 0.0016750843039174724</t>
+          <t>-0.002720048899755456 +/- 0.001321269335037733</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.0022616136919315077 +/- 0.0016750843039174546</t>
+          <t>-0.0025672371638141176 +/- 0.001347518807154541</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1171,92 +1171,92 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.0005806845965769858 +/- 0.0006330169675185816</t>
+          <t>4.4408920985006264e-17 +/- 0.0007486215595303135</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.003086797066014657 +/- 0.0009898615367177233</t>
+          <t>0.0023227383863080875 +/- 0.0009874996590099835</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-0.0034229828850856014 +/- 0.0014321973733325214</t>
+          <t>0.0006723716381418554 +/- 0.00127339038239607</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>-0.0006418092909535877 +/- 0.000890513587061936</t>
+          <t>0.0001833740831296171 +/- 0.0008665921075035368</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.002567237163814151 +/- 0.0010604738125243023</t>
+          <t>0.003575794621026929 +/- 0.0014008761169151487</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.0019559902200488753 +/- 0.0015951086003300784</t>
+          <t>0.0026589242053790207 +/- 0.0016347284988161854</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-0.002872860635696861 +/- 0.00290004307195023</t>
+          <t>0.004492665036674859 +/- 0.0014787249881910733</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-0.0007640586797066252 +/- 0.0013888224654647488</t>
+          <t>-0.0022616136919315077 +/- 0.0006583331060066574</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>3.056234718824546e-05 +/- 0.0001645832765016481</t>
+          <t>-0.00015281173594128283 +/- 0.00015281173594128283</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>-0.00311735941320298 +/- 0.001174167036204064</t>
+          <t>-0.00021393643031780707 +/- 0.000596553218091175</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.0008251833740830827 +/- 0.0012604884246516955</t>
+          <t>0.0010696821515892795 +/- 0.0006150553727841673</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-0.0003973105134474797 +/- 0.00078575550930209</t>
+          <t>3.0562347188289873e-05 +/- 0.0006758357086642912</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-0.002689486552567277 +/- 0.0007946210268948611</t>
+          <t>0.005409535452322767 +/- 0.001093858812235559</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>-0.00012224938875310398 +/- 0.0010062394641292378</t>
+          <t>-0.0014364303178483694 +/- 0.0012455796987967647</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-0.002383863080684634 +/- 0.001344743276283625</t>
+          <t>-0.0008557457212713504 +/- 0.0014897380937596565</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.00033618581907087777 +/- 0.00031908027227720823</t>
+          <t>0.00012224938875309287 +/- 0.0003667481662591768</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.00021393643031780707 +/- 0.0006120105255043096</t>
+          <t>0.0001833740831296171 +/- 0.0005501222493887464</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>-0.000702933985330112 +/- 0.00036290776549626684</t>
+          <t>0.0007334963325183574 +/- 0.0007128303049933135</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,52 +1266,52 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>-0.00012224938875308178 +/- 0.0004773991244441758</t>
+          <t>0.0007946210268949039 +/- 0.001006239464129235</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.0010085574572126666 +/- 0.0015824686388752668</t>
+          <t>-0.0014364303178483473 +/- 0.0012455796987967383</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-6.112469437651314e-05 +/- 0.00012224938875302627</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>-0.00033618581907094434 +/- 0.0004201628082172075</t>
+          <t>-0.0003056234718825879 +/- 0.00027335794345962705</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>-0.0006418092909535767 +/- 0.0006330169675185723</t>
+          <t>-0.002078239608801913 +/- 0.0012952090525927217</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.0006723716381417666 +/- 0.0010300916593125138</t>
+          <t>-0.002628361858190653 +/- 0.0013951970917498043</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>-0.0002750611246944201 +/- 0.0005195599022004988</t>
+          <t>-0.0011308068459657261 +/- 0.0007108620629347938</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>-0.000855745721271417 +/- 0.0008177926748324842</t>
+          <t>0.0010085574572127442 +/- 0.0008319472853799572</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>-0.002903422982885129 +/- 0.002539618876594395</t>
+          <t>-0.0013447432762835887 +/- 0.0013817426106916039</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>-0.0015892420537897522 +/- 0.0009449648431381715</t>
+          <t>-0.0014058679706601019 +/- 0.0004965793645865363</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.008463580064877563 +/- 0.002081279857103378</t>
+          <t>0.004246534945443858 +/- 0.0026184574320758636</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.011353583013860169 +/- 0.0009891188340459404</t>
+          <t>0.007342966676496643 +/- 0.0015405435430974946</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.004600412857564096 +/- 0.0016482676039495136</t>
+          <t>-0.0029489826010026254 +/- 0.0018369108230489562</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.00029489826010030694 +/- 0.0024317933504085245</t>
+          <t>-0.003479799469183109 +/- 0.00122160514168139</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.004924800943674379 +/- 0.0015992623843062482</t>
+          <t>-0.019463285166617474 +/- 0.0011112617918853664</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.007342966676496565 +/- 0.0025280539274724484</t>
+          <t>0.010115010321439133 +/- 0.001509752372299613</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.00044234739015035495 +/- 0.0004222300519987146</t>
+          <t>8.846947803011762e-05 +/- 0.0002963690834892535</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.00563255676791502 +/- 0.0017418978974488165</t>
+          <t>0.0033913299911531025 +/- 0.001359413809686356</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.02123267472721906 +/- 0.0033207167821313484</t>
+          <t>0.03099380713653792 +/- 0.0030317204915519804</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.016543792391624845 +/- 0.0028299479428212045</t>
+          <t>0.029165437923916283 +/- 0.002811449337709249</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.0019168386906516788 +/- 0.0014641334812511098</t>
+          <t>-0.00038336773813031356 +/- 0.001312545743690244</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-0.005691536419935172 +/- 0.0009873588347262428</t>
+          <t>0.003686228251253365 +/- 0.0005150176702026764</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.0150398112651135 +/- 0.0021630340101317824</t>
+          <t>-5.8979652020030306e-05 +/- 0.002213898481760353</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.015836036567384193 +/- 0.0016891776457233457</t>
+          <t>0.01902093777646714 +/- 0.0016902070045304916</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-0.00952521380123863 +/- 0.0022730133497544077</t>
+          <t>-0.004452963727513959 +/- 0.0017268553196057152</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.00911235623709814 +/- 0.0013922821154954818</t>
+          <t>-0.00026540843409019745 +/- 0.0012749021717025641</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.006133883810085472 +/- 0.001406884157107247</t>
+          <t>0.0053671483338248675 +/- 0.001290832711780537</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.010350928929519243 +/- 0.001025381223869879</t>
+          <t>0.0007077558242406523 +/- 0.0012101612815501866</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.006458271896195767 +/- 0.002095438386728445</t>
+          <t>-0.002713063992922393 +/- 0.001330641601023715</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00017693895606013532 +/- 0.00027027871984404813</t>
+          <t>0.00044234739015042157 +/- 0.0004011049987831176</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.007844293718667027 +/- 0.0015615691294454293</t>
+          <t>0.025036862282512572 +/- 0.0017666842584193852</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-0.003686228251253354 +/- 0.0007718226085698913</t>
+          <t>0.003774697729283427 +/- 0.001449508195511014</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.002772043644942446 +/- 0.0009156104214839198</t>
+          <t>0.004099085815393722 +/- 0.0010831240148750747</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.0004423473901503772 +/- 0.0007940378659885729</t>
+          <t>0.002034797994691873 +/- 0.0014947007841314326</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.004393984075493906 +/- 0.0018295579320844685</t>
+          <t>0.004128575641403754 +/- 0.0018604317659200757</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.00032438808611033875 +/- 0.0006108025708407138</t>
+          <t>0.0004128575641404009 +/- 0.0008465172571163141</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.016573282217634867 +/- 0.002365811987040016</t>
+          <t>0.01769389560601594 +/- 0.0022420026905040566</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-0.0018578590386317262 +/- 0.001818114142353079</t>
+          <t>-0.005868475375995252 +/- 0.0015177952500687129</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.00017693895606013532 +/- 0.0008151150080262658</t>
+          <t>-0.0017104099085815006 +/- 0.0013108882790264064</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00356826894721316 +/- 0.0011302723619426064</t>
+          <t>-0.010498378059569435 +/- 0.0017752777284921598</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.002182247124741921 +/- 0.0009344134189180037</t>
+          <t>0.0007667354762607159 +/- 0.0006072326830425731</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.0009731642583308275 +/- 0.0005445645919380423</t>
+          <t>3.3306690738754695e-17 +/- 0.0008022099975662189</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.0050132704217044745 +/- 0.0022497471097328945</t>
+          <t>-0.007107048068416366 +/- 0.0012332954093970145</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.008876437629018042 +/- 0.0012680625184311374</t>
+          <t>-0.0016219404305514384 +/- 0.0016902070045304684</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>-0.00020642878207021153 +/- 0.0007581810753277891</t>
+          <t>-0.0015924506045413844 +/- 0.0009798435697927388</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.002595104688882288 +/- 0.0006297303598956855</t>
+          <t>0.001857859038631704 +/- 0.0006731177947811005</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.0056915364199350725 +/- 0.0015097523722996538</t>
+          <t>0.0033618401651430594 +/- 0.0019658900987907795</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.0008846947803007654 +/- 0.0009231775784428521</t>
+          <t>-0.0036272485992332347 +/- 0.001560733544370305</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.0018283692126215944 +/- 0.0012497564199597355</t>
+          <t>0.002595104688882377 +/- 0.0011632605675798505</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.002034797994691784 +/- 0.0018008121074340343</t>
+          <t>0.002742553818932514 +/- 0.0016527462423122643</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.0033028605131230184 +/- 0.0016775538370189123</t>
+          <t>-0.005514597463874926 +/- 0.001874634629939587</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0009731642583308275 +/- 0.001960796250059497</t>
+          <t>0.0023002064287821144 +/- 0.0009851544139481163</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.003715718077263286 +/- 0.001286784089016302</t>
+          <t>-0.0030964317310527402 +/- 0.0011666199023799677</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.0038926570333234546 +/- 0.0012427783842940514</t>
+          <t>0.008846947803007987 +/- 0.0021870240304027416</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.00864051902093772 +/- 0.0014450014744912779</t>
+          <t>0.006605721026245981 +/- 0.0014697653546891425</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.005160719551754611 +/- 0.0012033149963493516</t>
+          <t>0.002654084340902407 +/- 0.0018321704001190448</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.0025361250368622357 +/- 0.0005927381669785202</t>
+          <t>0.0011501032143910628 +/- 0.0005348969963791646</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.0002654084340902085 +/- 0.0010669450023665919</t>
+          <t>-0.00020642878207014493 +/- 0.0016368845870100678</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.016809200825715076 +/- 0.0015825901344734506</t>
+          <t>-0.002388675906812121 +/- 0.0014108963390039276</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-0.0017988793866116736 +/- 0.0010253812238698794</t>
+          <t>-0.008611029194927722 +/- 0.0019102488635448648</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-0.012680625184311466 +/- 0.0017986376504838676</t>
+          <t>-0.0033028605131229295 +/- 0.001624886737122501</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.0005013270421704297 +/- 0.0009236484673173468</t>
+          <t>-0.00041285756414033425 +/- 0.0008257151282807279</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.00029489826010022926 +/- 0.0006978566538601709</t>
+          <t>0.0008257151282807573 +/- 0.0006297303598956689</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>-0.00011795930404013832 +/- 0.000577880210624158</t>
+          <t>0.0029194927749926825 +/- 0.00046534160536889317</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-0.0015924506045414733 +/- 0.0015391316249719735</t>
+          <t>-0.0008846947803007654 +/- 0.0016098312077801316</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.010586847537599475 +/- 0.00208712147204019</t>
+          <t>-0.0020937776467118475 +/- 0.0033738474670488897</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,92 +1616,92 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-0.00029489826010029583 +/- 0.00043740480608054955</t>
+          <t>0.0014450014744913254 +/- 0.0006386436988412935</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>0.0020937776467118362 +/- 0.0007740728250313439</t>
+          <t>0.0006192863462105791 +/- 0.0017715999169419837</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.011058684753759906 +/- 0.0007489486935535483</t>
+          <t>0.002034797994691873 +/- 0.0015573867209095955</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>-0.0007962253022707588 +/- 0.0005445645919380621</t>
+          <t>-0.0012090828664110486 +/- 0.0005664810590474288</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-0.0036567384252433445 +/- 0.0015503909676313644</t>
+          <t>0.002329696254792146 +/- 0.0015573867209095736</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-0.005780005897965246 +/- 0.0011049834264344142</t>
+          <t>-0.0020642878207018265 +/- 0.0020087745639547593</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-0.00017693895606020195 +/- 0.0013590939099738222</t>
+          <t>-0.001415511648481249 +/- 0.0014554954502215185</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-0.0025656148628723672 +/- 0.0006984794622428143</t>
+          <t>-0.0015629607785313747 +/- 0.0009785113549417234</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.00047183721616038675 +/- 0.00032838480464937207</t>
+          <t>0.00029489826010029583 +/- 0.00018651003598751687</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.003007962253022667 +/- 0.0017535911232460378</t>
+          <t>0.0008846947803007987 +/- 0.001318825112061207</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.0008846947803007654 +/- 0.001126804669686981</t>
+          <t>-0.00011795930404008281 +/- 0.0007126538468649081</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.0015039811265113 +/- 0.0011147778337620515</t>
+          <t>0.0015334709525214208 +/- 0.001053410268327458</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.0150693010911235 +/- 0.0017167537101536827</t>
+          <t>0.00356826894721326 +/- 0.0017468833051748683</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>-0.004305514597463922 +/- 0.0007934900647050189</t>
+          <t>0.002447655558832229 +/- 0.0016101012910313952</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.00976113240931874 +/- 0.0013670689456206783</t>
+          <t>0.0029489826010026922 +/- 0.0015604549165819039</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>-5.897965202007471e-05 +/- 0.0004899217848963765</t>
+          <t>-8.84694780300621e-05 +/- 0.00023032290403735047</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.0005013270421704186 +/- 0.0004578052107419585</t>
+          <t>-0.00035387791212027064 +/- 0.0008000389245797971</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.0025361250368622244 +/- 0.0009060626066491923</t>
+          <t>0.0011501032143910628 +/- 0.0008283439637386018</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.0019463285166617216 +/- 0.0004413633013003692</t>
+          <t>0.0032438808611029656 +/- 0.00045685442007755117</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.005013270421704463 +/- 0.0010550600896489957</t>
+          <t>-0.0015924506045413844 +/- 0.0016429829875769886</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1726,37 +1726,37 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>-0.0004718372161604534 +/- 0.0006213891921470475</t>
+          <t>0.0006192863462105791 +/- 0.00046534160536890727</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.0023296962547920573 +/- 0.000999613757397702</t>
+          <t>-0.0013565319964611744 +/- 0.0014031704221020467</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>-0.001356531996461252 +/- 0.0006072326830426022</t>
+          <t>-0.005750516071955147 +/- 0.0017656994845087098</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.0022707166027719937 +/- 0.0006467623768640728</t>
+          <t>-0.00029489826010022926 +/- 0.0004934591722406768</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.003833677381303391 +/- 0.0015152146952126459</t>
+          <t>0.004158065467413774 +/- 0.0013670689456206694</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.006310822766145641 +/- 0.0009156104214839283</t>
+          <t>0.00017693895606019083 +/- 0.0012455742897046777</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.0031554113830727704 +/- 0.0011725682897122348</t>
+          <t>0.0024476555588322513 +/- 0.0005756184398685881</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.0004735128736312433 +/- 0.0007739980367340505</t>
+          <t>-0.0035809411068363885 +/- 0.0007539354366887698</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.006629180230837495 +/- 0.0018959002519144121</t>
+          <t>-0.008256880733944982 +/- 0.0022633546972475774</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.0012429712932819914 +/- 0.0014056634610284731</t>
+          <t>0.0012133767386800498 +/- 0.0014097076488682517</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0038768866528559264 +/- 0.0016287763132071008</t>
+          <t>0.004912696063924238 +/- 0.0009188620713974689</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.0028706717963895125 +/- 0.0015266315923680208</t>
+          <t>2.9594554601952706e-05 +/- 0.0009943946502758885</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0018348623853211565 +/- 0.0016730741669254221</t>
+          <t>-0.002604320804971927 +/- 0.0012680843613867194</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.00029594554601956034 +/- 0.00029594554601957145</t>
+          <t>-8.878366380585812e-05 +/- 0.00029742159281209555</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.002278780704350358 +/- 0.0014681404859203597</t>
+          <t>-0.005978100029594558 +/- 0.0011214735319026975</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.010298905001479763 +/- 0.0030549838178310683</t>
+          <t>0.013909440662917993 +/- 0.003006433879656783</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.012488902042024307 +/- 0.0026197450105156462</t>
+          <t>0.017579165433560195 +/- 0.002876006064103324</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.0015093222846996768 +/- 0.0010031637322686327</t>
+          <t>0.005948505474992594 +/- 0.0012725658478839898</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.0008582420834566173 +/- 0.0012517482084969905</t>
+          <t>0.001686889612311304 +/- 0.0013435406289216882</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-0.0052974252737495895 +/- 0.001272565847884009</t>
+          <t>0.001390944066291777 +/- 0.0015437468311032543</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.01272565847883994 +/- 0.0006207806144836958</t>
+          <t>0.02095294465818285 +/- 0.002268572701596543</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.003551346552234447 +/- 0.0015377781659386284</t>
+          <t>0.011482687185557816 +/- 0.002100171056432105</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-0.0036697247706421353 +/- 0.0012144589836450323</t>
+          <t>-0.0038768866528559043 +/- 0.0014034809945403163</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.0014501331754956715 +/- 0.00131986404977672</t>
+          <t>-0.0034329683338266137 +/- 0.0014749850008140882</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.0007102693104469426 +/- 0.0009283449033062188</t>
+          <t>0.0013613495116898244 +/- 0.0007151847276468988</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-0.0008878366380585812 +/- 0.000990423233541356</t>
+          <t>-0.0024859425865641272 +/- 0.0005646281156655648</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-8.878366380585812e-05 +/- 0.00026635099141757433</t>
+          <t>0.00011837821840781082 +/- 0.00032955101289315896</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.0032554010062148197 +/- 0.0022067300245406543</t>
+          <t>-0.0013613495116898688 +/- 0.0014449903066864585</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.001686889612311404 +/- 0.0010592204893858067</t>
+          <t>0.0037289138798460852 +/- 0.001132354333809376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-0.002219591595146453 +/- 0.0013642415592324238</t>
+          <t>0.00366972477064218 +/- 0.001638159515016057</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.0012725658478839664 +/- 0.0008981350047643234</t>
+          <t>-0.0015981059485054906 +/- 0.0015558969432488993</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.0017460787215151873 +/- 0.0017075314278486714</t>
+          <t>0.0019828351583308533 +/- 0.0023898404537700574</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.0004584768684471699</t>
+          <t>-0.0012429712932820359 +/- 0.00041432376442736643</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.00029594554601958256 +/- 0.003103903072418316</t>
+          <t>0.002308375258952311 +/- 0.0016835114120541742</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-0.003225806451612856 +/- 0.001802354540229061</t>
+          <t>0.004587155963302736 +/- 0.0009657986902681994</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.0006806747558449789 +/- 0.0014318994262684957</t>
+          <t>0.004261615862681245 +/- 0.0015615159465253773</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.0026635099141757435 +/- 0.0016370898710789086</t>
+          <t>0.003048239124001151 +/- 0.0015437468311032872</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-0.00029594554601952705 +/- 0.0005294034868303638</t>
+          <t>0.0005918910920390541 +/- 0.0006065078878934249</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.0003847292098254296 +/- 0.00041957522576972783</t>
+          <t>0.0006806747558449122 +/- 0.00045943103569871986</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,272 +1936,272 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.003077833678603192 +/- 0.0007392717370107469</t>
+          <t>0.004320804971885172 +/- 0.0011167778789058008</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.0019236460491269148 +/- 0.0016060329743965733</t>
+          <t>0.003018644569399198 +/- 0.0013287922060162092</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2.2204460492503132e-17 +/- 0.00041853020490475746</t>
+          <t>-0.0007990529742527341 +/- 0.000577662660430406</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.000562296537437157 +/- 0.0007303322094852747</t>
+          <t>-0.00029594554601952705 +/- 0.0009358619888038835</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.00023675643681567716 +/- 0.0023668243886513494</t>
+          <t>0.0006510802012429595 +/- 0.0024325211705279047</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>-0.0023379698135542635 +/- 0.0013330696217289143</t>
+          <t>0.005090263391535943 +/- 0.0014666483212031909</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.00017756732761169401 +/- 0.0006235959605121641</t>
+          <t>-0.00011837821840781082 +/- 0.0006774503191630299</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.004942290618526146 +/- 0.001741055469675389</t>
+          <t>0.0009470257472624866 +/- 0.0013868451629310175</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.0023971589227581693 +/- 0.0006806747558449123</t>
+          <t>0.005652559928973067 +/- 0.0011722582018548937</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-0.0017164841669132457 +/- 0.001592616045821094</t>
+          <t>0.004587155963302725 +/- 0.002437736355159649</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-0.002426753477360133 +/- 0.00170932572692437</t>
+          <t>0.00272269902337966 +/- 0.0009245634419540323</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>-0.003314590115418703 +/- 0.0011896863712483822</t>
+          <t>-0.00017756732761172733 +/- 0.0012639335012762662</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.001065403965670364 +/- 0.0013639205234451657</t>
+          <t>0.004143237644273423 +/- 0.0013301097990082637</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.0032258064516128447 +/- 0.0009855475469278728</t>
+          <t>0.004172832198875398 +/- 0.0008922647784363359</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-5.9189109203883206e-05 +/- 0.0006722590524771158</t>
+          <t>-5.918910920390541e-05 +/- 0.0005583889394528814</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>-0.0021604024859425363 +/- 0.0015151140261817273</t>
+          <t>0.002219591595146464 +/- 0.001370646484392944</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>-0.002900266350991354 +/- 0.00157046453523783</t>
+          <t>0.002012429712932784 +/- 0.0011214735319026975</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.0024859425865641272 +/- 0.0018491268839080364</t>
+          <t>-0.0010358094110683891 +/- 0.0014269977450418853</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.001183782184078197 +/- 0.001153808149725845</t>
+          <t>0.00665877478543947 +/- 0.0011171699371516149</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.0020716188221368004 +/- 0.0005769040748629054</t>
+          <t>-0.0016277005031074432 +/- 0.0010853578467530413</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>-0.0009766203018644394 +/- 0.00032554010062147977</t>
+          <t>-0.00020716188221366893 +/- 0.0005134463324325883</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>-0.00026635099141757433 +/- 0.00027919446972644076</t>
+          <t>-0.0010654039656702973 +/- 0.00032955101289315896</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.006925125776857088 +/- 0.0013182040515726794</t>
+          <t>0.0068955312222550805 +/- 0.001538062913310001</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.00020716188221372444 +/- 0.0012419138951380725</t>
+          <t>0.0039656703166617065 +/- 0.001627431439463473</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>5.918910920390541e-05 +/- 0.00011837821840781082</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>-2.9594554601952706e-05 +/- 0.0005031074282331959</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.0006510802012429595 +/- 0.0009339883893494653</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.0036105356614382746 +/- 0.0018566898066123977</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>-0.0008878366380586034 +/- 0.0007003349846818332</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.005918910920390641 +/- 0.0011911578453683352</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>0.0011245930748741805 +/- 0.0023778999025274475</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-0.0013317549570879272 +/- 0.001595088840273692</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>0.0026931044687776963 +/- 0.0012656646806950406</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>-0.0007398638650488287 +/- 0.0004996135843780587</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>0.00041432376442733786 +/- 0.0008597714735918134</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>0.0031962118970108922 +/- 0.0006851634745658488</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>0.001006214856466392 +/- 0.0006510802012429595</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>0.005622965374371102 +/- 0.0016688809919942857</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>0.002900266350991365 +/- 0.0006722590524770844</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>0.0023971589227581693 +/- 0.0012090380713711234</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>-5.918910920390541e-05 +/- 0.00022146536766936217</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>0.0010654039656702973 +/- 0.0005488972178452523</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>-0.00032554010062147977 +/- 0.0004669941946747326</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>0.00011837821840783302 +/- 0.00035513465522347135</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>0.0023379698135543745 +/- 0.0008417557060270871</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>-0.001598105948505435 +/- 0.0012359048841563242</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.0004735128736313099 +/- 0.0006510802012430069</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0.00029594554601958256 +/- 0.0008265309289002285</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>0.0006806747558449789 +/- 0.0012971060669317207</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-0.0038768866528558267 +/- 0.0019516705645217524</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>-0.003403373779224561 +/- 0.0012433235594909514</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>0.00011837821840783302 +/- 0.00030180642282292284</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>-0.0032258064516128447 +/- 0.0007422276533876427</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>0.0026635099141758545 +/- 0.0011837821840781082</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>0.00029594554601957145 +/- 0.0007717315661678473</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>0.003314590115418814 +/- 0.002108495191542694</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>0.0008582420834566951 +/- 0.0009943946502759336</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>-0.00109499852027225 +/- 0.000805602698361406</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>0.0005918910920391207 +/- 0.00026470174341523155</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>-0.00011837821840777751 +/- 0.0008391504515394087</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>0.0006510802012430261 +/- 0.00039261613380949987</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>0.00142053862089373 +/- 0.0008658620206171962</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>0.004113643089671481 +/- 0.0011647628679582632</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>-0.00011837821840778861 +/- 0.0004987362990930299</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>0.0032849955608168615 +/- 0.00109499852027225</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>-2.9594554601952706e-05 +/- 8.878366380585811e-05</t>
-        </is>
-      </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.000443918319029335 +/- 0.00033087717926902707</t>
+          <t>0.00041432376442733786 +/- 0.0005799324635177588</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.0006806747558449899 +/- 0.0009996653302192893</t>
+          <t>-0.0006510802012429706 +/- 0.0006319667506381445</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.0004735128736313099 +/- 0.0008495235332588266</t>
+          <t>0.0006510802012429262 +/- 0.0020150393051848767</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>3.3306690738754695e-17 +/- 0.0005769040748629453</t>
+          <t>-0.00041432376442733786 +/- 0.00044293073533872434</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>-0.00038472920982535186 +/- 0.0007374925004070854</t>
+          <t>0.00029594554601952705 +/- 0.0007127312565132925</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>-0.0026339153595737906 +/- 0.0013655249476246367</t>
+          <t>0.0011837821840781193 +/- 0.0015937155392525887</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>-0.003018644569399176 +/- 0.0008349651364111056</t>
+          <t>-0.0006510802012429818 +/- 0.0012886381211646874</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.001477104874446078 +/- 0.000997456012770106</t>
+          <t>-0.007503692762186076 +/- 0.0011380419665735966</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.002392909896602646 +/- 0.0008192274519268522</t>
+          <t>-0.0007976366322008821 +/- 0.0007709298877813779</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.004638109305760685 +/- 0.0018261222405347723</t>
+          <t>-0.004135893648449018 +/- 0.0012180518834911784</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0007976366322008821 +/- 0.00063429573274989</t>
+          <t>0.002008862629246666 +/- 0.00144000680732099</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.003545051698670587 +/- 0.0010651554728106263</t>
+          <t>8.862629246676468e-05 +/- 0.0007120809922123419</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.0004135893648449018 +/- 0.0012050858525477716</t>
+          <t>-0.002629246676514019 +/- 0.0012141047319370404</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.00011816838995568624 +/- 0.00019596010578170652</t>
+          <t>-0.0004135893648449018 +/- 0.0003783234409118355</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.0025110782865583325 +/- 0.0015307824411263276</t>
+          <t>-0.006587887740029508 +/- 0.001167193280067256</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.021240768094534714 +/- 0.003248153283048592</t>
+          <t>0.02082717872968982 +/- 0.0028127117743323004</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.02744460856720825 +/- 0.0032292904447901844</t>
+          <t>0.023367799113737063 +/- 0.0013437595764306174</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-0.0029246676514032345 +/- 0.0008906832160520683</t>
+          <t>-0.0018316100443131367 +/- 0.0005878803173451195</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2.954209748892156e-05 +/- 0.0010523789146562354</t>
+          <t>-0.006528803545051665 +/- 0.0012634212573319342</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-0.004579025110782842 +/- 0.0017489819929826418</t>
+          <t>-0.005199409158050195 +/- 0.0011831600823929503</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-0.004608567208271764 +/- 0.0014544796011924498</t>
+          <t>-0.011462333825701564 +/- 0.0020671025919687808</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.0030428360413589208 +/- 0.0011368910726672825</t>
+          <t>0.007887740029542168 +/- 0.0014535792732812383</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.0013293943870014702 +/- 0.0007618196134846416</t>
+          <t>-0.0004431314623338234 +/- 0.0012551046254799345</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.0009158050221565684 +/- 0.0008708657591127679</t>
+          <t>0.0004135893648449018 +/- 0.0010585803761990443</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.0009748892171344114 +/- 0.00026587887740029407</t>
+          <t>-0.0007680945347119606 +/- 0.000701585943104157</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.0015361890694239211 +/- 0.0010044313146233329</t>
+          <t>0.001477104874446078 +/- 0.0009434989319155822</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>8.862629246676468e-05 +/- 0.0002307311573384524</t>
+          <t>-0.00011816838995568624 +/- 0.00023633677991137249</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0014475627769571565 +/- 0.001631248176340142</t>
+          <t>-0.0024224519940915677 +/- 0.001839218010785619</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0038995568685376457 +/- 0.000843891099384675</t>
+          <t>-0.0012407680945347055 +/- 0.0013589364844903916</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.0033382570162481364 +/- 0.0013015297354156913</t>
+          <t>-0.0003840472673559803 +/- 0.001032283911944228</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.0003545051698670587 +/- 0.0013843869440307145</t>
+          <t>0.0007090103397341174 +/- 0.0009992044032666278</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.000531757754800588 +/- 0.000843891099384675</t>
+          <t>0.004756277695716416 +/- 0.0015988253031297053</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.00017725258493352935 +/- 0.0003545051698670587</t>
+          <t>0.0008567208271787252 +/- 0.00042708514903399956</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.00815361890694235 +/- 0.000907668626040599</t>
+          <t>0.002511078286558344 +/- 0.0016983494655013222</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.00322008862629245 +/- 0.001631248176340142</t>
+          <t>-0.004756277695716371 +/- 0.0012141047319370406</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.004313146233382548 +/- 0.0008480177308364696</t>
+          <t>0.0028064992614475594 +/- 0.0011460658635906106</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0014475627769571565 +/- 0.0009748892171344115</t>
+          <t>0.00487444608567209 +/- 0.000868859153314828</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0002067946824224509 +/- 0.0002307311573384524</t>
+          <t>-0.0003840472673559803 +/- 0.0006612416332525635</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.00047267355982274497 +/- 0.0004007285071270448</t>
+          <t>-0.000531757754800588 +/- 0.00039192021156341303</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,122 +2381,122 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.0020384047267355877 +/- 0.0010271987385946008</t>
+          <t>0.004076809453471208 +/- 0.001142633950121969</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.0024519940915804896 +/- 0.0010898591873380575</t>
+          <t>-0.0015657311669128426 +/- 0.0010407039854539702</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>-0.0001477104874446078 +/- 0.0003027164184921579</t>
+          <t>0.000738552437223039 +/- 0.0003302906909157722</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.00017725258493352935 +/- 0.000442145629160877</t>
+          <t>0.0008271787296898036 +/- 0.000368980679373611</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.0003545051698670587 +/- 0.0007450233508371301</t>
+          <t>0.0006203840472673528 +/- 0.0009748892171344114</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.0004135893648449018 +/- 0.0006224906205525958</t>
+          <t>0.0016543574593796072 +/- 0.0007838404231268261</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.00023633677991137249 +/- 0.00039192021156341303</t>
+          <t>-5.908419497784312e-05 +/- 0.0003445170986614635</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.004342688330871469 +/- 0.0007821685255464494</t>
+          <t>-0.001270310192023627 +/- 0.00110575877531538</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.005317577548005881 +/- 0.0010974402139442608</t>
+          <t>0.002688330871491862 +/- 0.000992632060053847</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-0.0004135893648449018 +/- 0.001597460069080733</t>
+          <t>-0.0014180206794682348 +/- 0.0009416471167213675</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-0.006499261447562743 +/- 0.0010061675843974188</t>
+          <t>0.0011816838995568624 +/- 0.0010569302109304712</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.0054357459379615666 +/- 0.0010250724710722235</t>
+          <t>0.002806499261447548 +/- 0.0009820248235506395</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0022451994091580384 +/- 0.0008165598204481644</t>
+          <t>-0.00017725258493352935 +/- 0.0007612466012836076</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.0012407680945347055 +/- 0.0009229246293538096</t>
+          <t>0.006174298375184706 +/- 0.0009748892171344313</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.00017725258493352935 +/- 0.00042194554969233756</t>
+          <t>0.00017725258493352935 +/- 0.00014472612955882807</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.00322008862629245 +/- 0.0007976366322008821</t>
+          <t>0.0022451994091580384 +/- 0.0010250724710722235</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.001063515509601176 +/- 0.0009360696908570031</t>
+          <t>2.954209748892156e-05 +/- 0.0008808302225037221</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.0018611521418020582 +/- 0.0013796507449140981</t>
+          <t>-0.0054357459379615666 +/- 0.0010830311834459832</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.0013589364844903916 +/- 0.000981580367848512</t>
+          <t>0.0027769571639586267 +/- 0.0005636272977352678</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>2.954209748892156e-05 +/- 0.0006397757113059852</t>
+          <t>-0.0008862629246676468 +/- 0.0006336074029402396</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.0003249630723781372 +/- 0.0005358451151319634</t>
+          <t>0.0008271787296898036 +/- 0.00036898067937361095</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.0001477104874446078 +/- 0.0002723646811607929</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.002540620384047254 +/- 0.0010335512959843904</t>
+          <t>0.007740029542097559 +/- 0.0011272545954705356</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.004342688330871469 +/- 0.000953161938251202</t>
+          <t>-0.0011225997045790192 +/- 0.0006308465732367064</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2506,92 +2506,92 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>2.954209748892156e-05 +/- 0.0005022156573116666</t>
+          <t>-2.954209748892156e-05 +/- 0.0003355337279645639</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.0012112259970457838 +/- 0.000956817414517079</t>
+          <t>0.0017725258493352936 +/- 0.0010233682762593017</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.0027178729689807833 +/- 0.000756646881823671</t>
+          <t>0.0007680945347119606 +/- 0.0011225997045790192</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>-0.0001477104874446078 +/- 0.0003027164184921579</t>
+          <t>0.0 +/- 0.0002954209748892156</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.00011816838995568624 +/- 0.0008376630356725408</t>
+          <t>0.001802067946824215 +/- 0.0007641073652217132</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.000738552437223039 +/- 0.0010507190099721506</t>
+          <t>0.001270310192023627 +/- 0.0013605410859284365</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.000738552437223039 +/- 0.0006768944896537395</t>
+          <t>0.002127031019202352 +/- 0.0008743662385198621</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.0013884785819793133 +/- 0.0009802457916122287</t>
+          <t>0.0003840472673559803 +/- 0.0010573429936882237</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.00017725258493352935 +/- 0.00027075779586149573</t>
+          <t>-0.00023633677991137249 +/- 0.00017725258493352935</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>-0.0007090103397341174 +/- 0.0005636272977352677</t>
+          <t>-2.954209748892156e-05 +/- 0.0008505867089446318</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.0004431314623338234 +/- 0.0006090259417455892</t>
+          <t>-0.0009158050221565684 +/- 0.0006532745757015027</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.908419497784312e-05 +/- 0.00028945225911765614</t>
+          <t>-0.0003545051698670587 +/- 0.00043417838867648424</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.001004431314623333 +/- 0.0009172333646239257</t>
+          <t>-0.0004431314623338234 +/- 0.0012894034175949826</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.0015952732644017643 +/- 0.0006083090186698344</t>
+          <t>-0.0007680945347119606 +/- 0.0007260387431281799</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>-5.908419497784312e-05 +/- 0.001038605366691099</t>
+          <t>0.0007090103397341174 +/- 0.0008376630356725408</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>2.954209748892156e-05 +/- 8.862629246676468e-05</t>
+          <t>0.00017725258493352935 +/- 0.00032896687520413544</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.0004431314623338234 +/- 0.0003027164184921579</t>
+          <t>0.0003249630723781372 +/- 0.0004470530561424365</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.00011816838995568624 +/- 0.00019596010578170652</t>
+          <t>-0.0005022156573116666 +/- 0.0005455298467538935</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2601,52 +2601,52 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>5.908419497784312e-05 +/- 0.00031817812745255395</t>
+          <t>-0.000531757754800588 +/- 0.00031817812745255395</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.0027178729689807833 +/- 0.0012308813386114948</t>
+          <t>-0.0009453471196454899 +/- 0.0013065491514030055</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>8.862629246676468e-05 +/- 0.0001353788979307479</t>
+          <t>-2.954209748892156e-05 +/- 8.862629246676468e-05</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>5.908419497784312e-05 +/- 0.0002210728145804385</t>
+          <t>0.0008271787296898036 +/- 0.0005573991806237255</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>-0.0015066469719349994 +/- 0.0007169666823935914</t>
+          <t>0.0005908419497784312 +/- 0.0009248139345641622</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>-2.954209748892156e-05 +/- 0.000956817414517079</t>
+          <t>0.0005612998522895096 +/- 0.0011923448195338528</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.0005612998522895096 +/- 0.00027869959031186274</t>
+          <t>0.0012998522895125487 +/- 0.0003289668752041355</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>-0.0016248153618906858 +/- 0.000999641023083518</t>
+          <t>-0.0017725258493352936 +/- 0.001353788979307479</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.0018906942392909799 +/- 0.0013025351660294526</t>
+          <t>-0.0011816838995568624 +/- 0.0007236306477941404</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>-0.0003840472673559803 +/- 0.0006743109134719804</t>
+          <t>-0.0002067946824224509 +/- 0.0010737241858426087</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.003907637655417406 +/- 0.0010065127294257047</t>
+          <t>-0.002871521610420302 +/- 0.0010086870951687764</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.0007696862048549358 +/- 0.0009565123991357981</t>
+          <t>-0.005535820011841275 +/- 0.001577887267168319</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.0018650088809946896 +/- 0.0012493160358797645</t>
+          <t>0.00316755476613384 +/- 0.001343938361493933</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.0018058022498519844 +/- 0.0013723300161633102</t>
+          <t>-0.00577264653641203 +/- 0.0012715649256906283</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.003285968028419206 +/- 0.0014225001511822234</t>
+          <t>-0.0023386619301361323 +/- 0.0007882490796740131</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0020130254588513695 +/- 0.0014429908356369387</t>
+          <t>0.0004440497335702065 +/- 0.0009003496936498249</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-5.92066311426942e-05 +/- 0.0003927323612025083</t>
+          <t>-8.88099467139858e-05 +/- 0.00041969943394782694</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.010864416814683264 +/- 0.0015442038313493202</t>
+          <t>-0.0034339846062758418 +/- 0.0009565123991358118</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.00432208407341621 +/- 0.0014271131785901802</t>
+          <t>0.002072232089994119 +/- 0.0013694533459112155</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.00331557134399052 +/- 0.0017653110143132616</t>
+          <t>0.0037892243931320624 +/- 0.0016257584627289514</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-0.010834813499111917 +/- 0.0013771111130388195</t>
+          <t>-0.014653641207815237 +/- 0.0019105035879529364</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-0.0017761989342806594 +/- 0.001075541866464476</t>
+          <t>-0.001006512729425657 +/- 0.0011171084821855186</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-0.004470100651272957 +/- 0.0009678971417567683</t>
+          <t>0.001184132622853795 +/- 0.001042440311525119</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-0.003966844286560101 +/- 0.0030079066420084315</t>
+          <t>-0.015571343990526908 +/- 0.003111025377245635</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.004410894020130252 +/- 0.00260256753748666</t>
+          <t>0.00429248075784493 +/- 0.0019378304143343025</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.0018650088809946674 +/- 0.0008058411834704643</t>
+          <t>-0.0008880994671402909 +/- 0.0010997143647724537</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-0.003137951450562482 +/- 0.0017220887592953127</t>
+          <t>-0.0013617525162817779 +/- 0.0007965437564874921</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.008644168146832443 +/- 0.00143690480752063</t>
+          <t>-0.008851391355831817 +/- 0.001494601013779091</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.0014505624629958746 +/- 0.0014887259870550844</t>
+          <t>-0.0009177027827116047 +/- 0.0012521187674693086</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.0002368265245707546 +/- 0.0002580757219384615</t>
+          <t>0.0001776198934280826 +/- 0.00014502603568877654</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.009029011249259911 +/- 0.0014992844596922138</t>
+          <t>-0.014920071047957307 +/- 0.0013834602066960142</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.0019834221432800335 +/- 0.0013825097014606984</t>
+          <t>-0.00355239786856123 +/- 0.0008579855977613622</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.002634695085849614 +/- 0.0010872923429370556</t>
+          <t>0.004055654233274175 +/- 0.001220934909846145</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.0033747779751332253 +/- 0.0011856118646832838</t>
+          <t>0.004174067495559553 +/- 0.0010545596880140373</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.0034931912374185914 +/- 0.0009977678831469907</t>
+          <t>0.0006216696269982669 +/- 0.0008209250813417385</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.00011841326228535509 +/- 0.0005801041427550392</t>
+          <t>0.0002960331557134932 +/- 0.0007605229472270844</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.012907045589105982 +/- 0.0016439838220147836</t>
+          <t>0.0019538188277087643 +/- 0.0017016113514742163</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-0.022380106571936065 +/- 0.0022900035057209925</t>
+          <t>-0.030609828300769627 +/- 0.0028245969074899963</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-0.0031379514505624705 +/- 0.0009746641582684615</t>
+          <t>-0.013913558318531628 +/- 0.0016375745039596697</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.001716992303137954 +/- 0.0008139566065640963</t>
+          <t>-0.005979869745411437 +/- 0.000813956606564106</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2.96033155713471e-05 +/- 0.00040697830328202434</t>
+          <t>2.9603315571380406e-05 +/- 0.00042797016858498653</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.0006216696269982335 +/- 0.00038484310242746533</t>
+          <t>0.0010065127294257349 +/- 0.0005490597096208354</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,122 +2826,122 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.008259325044404986 +/- 0.0015911610006366695</t>
+          <t>-0.002220248667850755 +/- 0.0004633651818383249</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.02101835405565422 +/- 0.002394028018846134</t>
+          <t>-0.02072232089994074 +/- 0.0015941873318930022</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>-0.0006512729425695585 +/- 0.000526240048390498</t>
+          <t>0.0008288928359976855 +/- 0.00031883746637859344</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.001332149200710475 +/- 0.000860535337699723</t>
+          <t>-0.0025162818235641925 +/- 0.0013255543621810732</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.0018650088809946564 +/- 0.0014625955390213908</t>
+          <t>-0.001332149200710453 +/- 0.001215179144569205</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>-0.002841918294849033 +/- 0.0010690035574463029</t>
+          <t>-0.006068679692125478 +/- 0.0007518309709414097</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>0.0024274718768502066 +/- 0.0006181353764896545</t>
+          <t>0.0002072232089994519 +/- 0.0006885555565194285</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.0032563647128478258 +/- 0.0008579855977613622</t>
+          <t>0.0021610420367081497 +/- 0.0009272030647345233</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.004558910597986987 +/- 0.0009095495260945703</t>
+          <t>-0.011634103019538145 +/- 0.0012352069890482597</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-0.001657785671995271 +/- 0.0012712202814437</t>
+          <t>-0.001095322676139665 +/- 0.0010259161309155258</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.002131438721136769 +/- 0.0013291855725662276</t>
+          <t>-0.001539372409709827 +/- 0.0010820406679986373</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.0010361160449970375 +/- 0.0009751136229722132</t>
+          <t>-0.0023386619301361323 +/- 0.0009215146486840352</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-0.0009473060982830072 +/- 0.0007104795737122601</t>
+          <t>-0.004262877442273471 +/- 0.0009380094445089026</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.0068679692125517946 +/- 0.000961993890424628</t>
+          <t>-0.003049141503848396 +/- 0.0007948917455356784</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.0009177027827116713 +/- 0.0005686611223297386</t>
+          <t>-0.0005032563647128008 +/- 0.0006492513972605468</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>0.0015689757252812298 +/- 0.0015667399197631003</t>
+          <t>-0.004114860864416758 +/- 0.0013268759521027388</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.002841918294849011 +/- 0.0018401740992208505</t>
+          <t>0.004854943753700469 +/- 0.000947306098283008</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.00370041444641801 +/- 0.00133871155175783</t>
+          <t>-0.0017761989342805929 +/- 0.0013370739834974625</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.000799289520426294 +/- 0.001498114970856131</t>
+          <t>-0.005180580224985132 +/- 0.001633555910162405</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-0.0013025458851391503 +/- 0.0007512479301627961</t>
+          <t>-0.00198342214328 +/- 0.00047825619956790526</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>-0.0010065127294256794 +/- 0.0005801041427550517</t>
+          <t>-0.000710479573712186 +/- 0.00042281991880064175</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>-0.0007400828892835775 +/- 0.0005655705498680563</t>
+          <t>-0.001065719360568318 +/- 0.0004430618575220762</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-0.0026642984014209614 +/- 0.0027548585255492775</t>
+          <t>-0.010864416814683187 +/- 0.001249316035879769</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.014476021314387211 +/- 0.0016821874061782496</t>
+          <t>0.00669034931912379 +/- 0.0013771111130388355</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2951,92 +2951,92 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>0.0010953226761397205 +/- 0.0006757082421855103</t>
+          <t>-2.9603315571302692e-05 +/- 0.0004671324404398931</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>0.003197158081705154 +/- 0.0011826515308133877</t>
+          <t>-0.0028419182948489774 +/- 0.0011326895482361792</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-0.00461811722912967 +/- 0.0008393988678956729</t>
+          <t>0.0026050917702783115 +/- 0.0012405166867825398</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>-0.0003256364712847959 +/- 0.0007770517909062595</t>
+          <t>-0.0002664298401420684 +/- 0.0006131532024040174</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.002901124925991727 +/- 0.0015541035818124977</t>
+          <t>-0.006009473060982773 +/- 0.00136336044282646</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>2.9603315571335997e-05 +/- 0.0014828276834065587</t>
+          <t>0.00538780343398465 +/- 0.0010657193605683765</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>0.0032859680284191726 +/- 0.0013001889435167336</t>
+          <t>-0.001391355831853125 +/- 0.0005928059323416407</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>0.002605091770278256 +/- 0.0014490513026074888</t>
+          <t>-0.000651272942569514 +/- 0.0015083172531506145</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>8.88099467140413e-05 +/- 0.00018955370744326585</t>
+          <t>-0.0004144464179987706 +/- 0.000271318868854692</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.0015985790408525658 +/- 0.0008900708335330272</t>
+          <t>-0.0023682652457074683 +/- 0.0011465314820033711</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.004381290704558916 +/- 0.0015930875129749906</t>
+          <t>-0.004647720544700962 +/- 0.001256311141144044</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-0.0015985790408525658 +/- 0.0007512479301628004</t>
+          <t>8.88099467140746e-05 +/- 0.0009366069875403458</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.007341622261693303 +/- 0.0012119295139407093</t>
+          <t>0.0008288928359976744 +/- 0.001023778357950892</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>-0.0031379514505624705 +/- 0.0012503677964442103</t>
+          <t>-0.0030787448194197096 +/- 0.0016860900966131586</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>0.005002960331557138 +/- 0.001535096762873199</t>
+          <t>0.0032563647128478813 +/- 0.0010339993603654786</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>0.00011841326228536619 +/- 0.00044306185752208515</t>
+          <t>0.0002368265245707768 +/- 0.0001776198934280826</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0.0015689757252812298 +/- 0.0011159311323251082</t>
+          <t>-0.0007104795737122082 +/- 0.0007965437564874848</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>-0.0014801657785671995 +/- 0.0008979130188338086</t>
+          <t>-0.0008288928359975634 +/- 0.0012334320104203465</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3046,52 +3046,52 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-0.00032563647128478477 +/- 0.000788249079674017</t>
+          <t>-0.0007696862048548914 +/- 0.0005328596802841873</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>0.0002368265245707546 +/- 0.0011900385578592044</t>
+          <t>-0.0007992895204262274 +/- 0.00045956704251806483</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.00020722320899937418 +/- 0.00023120928584682634</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0004144464179988039 +/- 0.0004228199188006402</t>
+          <t>0.0011841326228538064 +/- 0.0002960331557134266</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>-0.0010361160449970375 +/- 0.001185981386856733</t>
+          <t>5.9206631142738606e-05 +/- 0.0011752180723078314</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>-0.0007104795737122749 +/- 0.001109235878933991</t>
+          <t>0.0033747779751332695 +/- 0.0014694699403186328</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>0.0010361160449970485 +/- 0.0012507181867541495</t>
+          <t>0.0004736530491415536 +/- 0.0010852754754187858</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>0.0036708111308466408 +/- 0.0011092358789340042</t>
+          <t>-0.0024570751924214984 +/- 0.0009911586170978802</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>-0.002101835405565422 +/- 0.0014649902938612923</t>
+          <t>0.004884547069271816 +/- 0.0011017047996405038</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>-0.0032563647128478258 +/- 0.0011388622890273275</t>
+          <t>-0.00011841326228532179 +/- 0.000751247930162783</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.0012535255405828449 +/- 0.0007415957108241448</t>
+          <t>-0.005954246317768741 +/- 0.001687610406497817</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.0009088060169225476 +/- 0.0014459758063377316</t>
+          <t>-0.0017862738953306478 +/- 0.0008979347403255681</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0037605766217487123 +/- 0.0013944591326409757</t>
+          <t>-0.005202130993419008 +/- 0.0017627528812817572</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.0031024757129426207 +/- 0.0008105620279772729</t>
+          <t>0.0032591664055155014 +/- 0.0008075273410670688</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0014102162331557921 +/- 0.0012710310116372926</t>
+          <t>-0.0019743027264180644 +/- 0.0011978385994118714</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.0015982450642431534 +/- 0.0010986241393267481</t>
+          <t>-0.005703541209652163 +/- 0.0012981708039616533</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.133813851456946e-05 +/- 9.401441554370838e-05</t>
+          <t>0.0005014102162331224 +/- 0.00031958755961095266</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.001441554371670295 +/- 0.0010783234430639618</t>
+          <t>-0.0019429645879035062 +/- 0.0013573430164655375</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.0020996552804763867 +/- 0.0016226378522092785</t>
+          <t>0.0033531808210592205 +/- 0.002403249084304356</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.02400501410216236 +/- 0.004150854450591898</t>
+          <t>0.01150109683484799 +/- 0.0028689376910462695</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-0.0018802883108742896 +/- 0.0014360939188203786</t>
+          <t>0.0028831087433406344 +/- 0.0009587626788328689</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-0.0006581009088059808 +/- 0.0011595111250391743</t>
+          <t>-0.0007834534628643252 +/- 0.0017685930503945548</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.00645565653400193 +/- 0.0008774678784080295</t>
+          <t>0.000846129739893442 +/- 0.0017167465903857476</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-0.0015042306486994228 +/- 0.001578148331183218</t>
+          <t>-0.008962707615167686 +/- 0.002216827224547477</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.005891570040739624 +/- 0.0011539926442821645</t>
+          <t>-0.00012535255405828893 +/- 0.0012628919886938082</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.0009401441554372058 +/- 0.001180911543805485</t>
+          <t>-0.004982764023816988 +/- 0.000798354071003271</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.001410216233155781 +/- 0.000963361087366944</t>
+          <t>-0.0004700720777185641 +/- 0.0011994772302729335</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.002036979003447237 +/- 0.001524013339490771</t>
+          <t>-0.002601065496709509 +/- 0.0008414742451956991</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-0.00040739580068938075 +/- 0.000897934740325566</t>
+          <t>-0.004011281729865268 +/- 0.0012597775770756459</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.00034471952366034176 +/- 0.0002603141292045988</t>
+          <t>-0.0005327483547477252 +/- 0.00037211977709302466</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>9.401441554376388e-05 +/- 0.000875787440456424</t>
+          <t>-0.0044186775305547045 +/- 0.0017247368105066697</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-0.001128172986524556 +/- 0.0004250911929254435</t>
+          <t>-0.0029457850203697955 +/- 0.001050645854856802</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.000313381385145739 +/- 0.0007927991626871524</t>
+          <t>-0.0012535255405828893 +/- 0.001129912652918814</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.0004700720777186085 +/- 0.00047007207771858627</t>
+          <t>-0.0003760576621748779 +/- 0.0008147916013788751</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.0012848636790975033 +/- 0.0007605553807277528</t>
+          <t>0.0004387339392039946 +/- 0.0007309247126098712</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>3.3306690738754695e-17 +/- 0.00024274417713618049</t>
+          <t>-0.00021936696960201952 +/- 0.0004442947940695015</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.004073958006894441 +/- 0.0010008598823360324</t>
+          <t>0.006612347226574722 +/- 0.0012802693961651809</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-6.267627702909451e-05 +/- 0.0008841576922385305</t>
+          <t>0.0003760576621748446 +/- 0.0014070789295295184</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-0.0012848636790974254 +/- 0.0011251220978386804</t>
+          <t>0.0003133813851456946 +/- 0.0009810389120964238</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.002350360388592965 +/- 0.001078778720028737</t>
+          <t>-0.0008774678784080559 +/- 0.0009988954842061657</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-3.133813851453615e-05 +/- 0.000618084704585258</t>
+          <t>0.0009401441554371503 +/- 0.0005053123001127299</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.0001566906925729028 +/- 0.0001566906925729028</t>
+          <t>-0.00031338138514572786 +/- 0.000313381385145739</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.0011281729865246337 +/- 0.001096387068914811</t>
+          <t>-0.004763397054214991 +/- 0.0009587626788328675</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.0010341585709808365 +/- 0.0008869302223807555</t>
+          <t>-0.002507051081165801 +/- 0.0008524895336092433</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>5.551115123125783e-17 +/- 0.0004431882050683548</t>
+          <t>-0.0010028204324663338 +/- 0.00048142561879464867</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.00015669069257291391 +/- 0.0003503710400344576</t>
+          <t>6.267627702912781e-05 +/- 0.00036546235630492745</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.0016922594797869396 +/- 0.001223392121337697</t>
+          <t>-0.0028831087433406565 +/- 0.0006236210824861202</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-0.0014728925101848533 +/- 0.0011896115885993395</t>
+          <t>-0.0032278282670009538 +/- 0.001261724985220777</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0.00040739580068948066 +/- 0.0003721197770930125</t>
+          <t>-0.0004073958006894474 +/- 0.0004442947940695086</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.001128172986524567 +/- 0.001677102871859561</t>
+          <t>-0.00031338138514572786 +/- 0.0014084741494355458</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.001848950172359709 +/- 0.0012092623868113273</t>
+          <t>0.001692259479786884 +/- 0.0016535137522122256</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0008461297398934975 +/- 0.0009510492576304168</t>
+          <t>-0.001284863679097481 +/- 0.001531726657455324</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-0.0006267627702914002 +/- 0.0010945941207504265</t>
+          <t>-0.0030711375744280956 +/- 0.0015146406735937988</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.004136634283923568 +/- 0.00105623939494532</t>
+          <t>-0.003353180821059243 +/- 0.0009195487778828707</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-0.002632403635224034 +/- 0.0013529948696285276</t>
+          <t>-0.0027577561892823677 +/- 0.0015467204862742903</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.0006581009088059697 +/- 0.0009448331828067316</t>
+          <t>-0.0001566906925728917 +/- 0.0012237934308847807</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.00021936696960204172 +/- 0.0003976364005155102</t>
+          <t>0.0001566906925728584 +/- 0.0005101479346944226</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-0.000219366969601964 +/- 0.0009088060169225924</t>
+          <t>-0.007991225321215944 +/- 0.001239739294569267</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>-0.000658100908805992 +/- 0.0008913483330196166</t>
+          <t>-0.01429019116264495 +/- 0.0014306126243200685</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.0018176120338452173 +/- 0.0012519576531142688</t>
+          <t>-0.005327483547477285 +/- 0.0018056860283156466</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.0003133813851457723 +/- 0.001010624600225456</t>
+          <t>-0.005640864932623025 +/- 0.0016223352059598537</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>0.0003133813851457612 +/- 0.0004648197108803336</t>
+          <t>6.267627702912781e-05 +/- 0.0004387339392039898</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.0006581009088060475 +/- 0.0005139836874602714</t>
+          <t>-0.00012535255405828893 +/- 0.0005978935765696961</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.0004073958006895029 +/- 0.000506283121949327</t>
+          <t>-0.0010654967094954726 +/- 0.0004475981465711587</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.0026010654967095538 +/- 0.0010950426330088487</t>
+          <t>0.0001566906925728473 +/- 0.0023503603885929123</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.0008461297398933976 +/- 0.001156118254195973</t>
+          <t>-0.005797555625195882 +/- 0.0016238478731471781</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,92 +3396,92 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>0.00034471952366034176 +/- 0.0004742320887001396</t>
+          <t>0.00028204324663113625 +/- 0.0003559328327044875</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>0.0006581009088060585 +/- 0.0007342760585308734</t>
+          <t>0.00445001566906923 +/- 0.0012519576531142575</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>0.0018176120338452395 +/- 0.0006979334832754769</t>
+          <t>-0.0005954246317768752 +/- 0.002013704020860826</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.0010654967094954949 +/- 0.0004475981465711525</t>
+          <t>-0.0012221874020683198 +/- 0.0008105620279772892</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-0.001128172986524567 +/- 0.0014374609766442878</t>
+          <t>-0.0015355687872140255 +/- 0.0010341585709808833</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-0.000407395800689403 +/- 0.0011128349047047838</t>
+          <t>-0.007803196490128528 +/- 0.001851073572625798</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>0.0005327483547477696 +/- 0.0006581009088059925</t>
+          <t>0.001504230648699445 +/- 0.0012201768933833748</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>0.005609526794108477 +/- 0.0009022989689055532</t>
+          <t>-0.0047007207771858515 +/- 0.0018056860283156275</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>0.0001566906925729028 +/- 0.000252656150056389</t>
+          <t>-0.0002193669696019973 +/- 0.0002006619942786901</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.002225007834534598 +/- 0.0012011136256180944</t>
+          <t>-0.004042619868379815 +/- 0.0013834998467342008</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>-0.00018802883108739454 +/- 0.0008195986731822059</t>
+          <t>-0.001034158570980903 +/- 0.0010303530067548375</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.00159824506424322 +/- 0.000720777185835167</t>
+          <t>0.0002193669696019973 +/- 0.0006581009088060131</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-0.002162331557505448 +/- 0.002042756313097131</t>
+          <t>0.001692259479786884 +/- 0.0016052959542294924</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0.0018176120338452173 +/- 0.0007118656654089946</t>
+          <t>0.0016609213412723035 +/- 0.0013299338874285917</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-0.0012221874020682867 +/- 0.0016007010704007741</t>
+          <t>-0.01081165778752744 +/- 0.0014914451938941612</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>0.00012535255405832224 +/- 0.00025070510811660285</t>
+          <t>-0.00012535255405830004 +/- 0.0003760576621748631</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>-9.401441554366397e-05 +/- 0.00039763640051550757</t>
+          <t>-0.003290504544030104 +/- 0.0006610787561807885</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>0.0007207771858352196 +/- 0.0007153063121600412</t>
+          <t>-0.00025070510811657786 +/- 0.00053916172153196</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>-0.00015669069257283618 +/- 0.00028892336124389364</t>
+          <t>-0.0008147916013789058 +/- 0.0003489667416377275</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>0.0028517706048261315 +/- 0.0013328843822085048</t>
+          <t>0.0016609213412723256 +/- 0.0017394784188502581</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3506,37 +3506,37 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>6.267627702919443e-05 +/- 0.00043873393920402</t>
+          <t>0.00012535255405827784 +/- 0.00028721878376405106</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.002413036665622104 +/- 0.0011303471511671047</t>
+          <t>-0.0006267627702914557 +/- 0.0013803018204666287</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>-3.133813851453615e-05 +/- 0.0009448331828067368</t>
+          <t>-0.0013162018176120394 +/- 0.00100867921901793</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>-0.0005954246317768308 +/- 0.0004742320887001528</t>
+          <t>-0.0004700720777186085 +/- 0.00047007207771858627</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>-0.0021623315575054368 +/- 0.0009448331828067111</t>
+          <t>0.004167972422438071 +/- 0.0010769564573763464</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>-0.0014728925101848533 +/- 0.0011729844733446009</t>
+          <t>-0.0030711375744281065 +/- 0.0011708894824361703</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>0.0020056408649326563 +/- 0.0007828264491881272</t>
+          <t>-0.00034471952366031954 +/- 0.0008344423037100928</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.00608424336973481 +/- 0.0008046051143979722</t>
+          <t>-0.0030265210608424464 +/- 0.0015789804591425966</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.0022464898595943917 +/- 0.0017639056505588295</t>
+          <t>-0.0034009360374415154 +/- 0.0018217361094533418</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.010202808112324513 +/- 0.0015851339526840127</t>
+          <t>-0.0005616224648986257 +/- 0.0014216269266638906</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0015912636505460264 +/- 0.0010296411856474202</t>
+          <t>0.003806552262090457 +/- 0.0011489518027782775</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0005928237129484981 +/- 0.0015628679920584277</t>
+          <t>0.003400936037441482 +/- 0.0016653985828496104</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.0008736349453978276 +/- 0.0015835978209609357</t>
+          <t>-0.004243369734789415 +/- 0.001939503309568815</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.00018720748829955668 +/- 0.0003474423939363635</t>
+          <t>0.0005928237129484981 +/- 0.0005304212168486827</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.002059282371294846 +/- 0.000544012348647828</t>
+          <t>-0.013666146645865861 +/- 0.0019071084917237015</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.0032137285491419254 +/- 0.002573110005618634</t>
+          <t>0.011357254290171592 +/- 0.0015737310718150928</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.010358814352574065 +/- 0.00300829224167088</t>
+          <t>0.009703588143525722 +/- 0.004121518347150694</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-0.00430577223088926 +/- 0.0015208808245808518</t>
+          <t>0.005897035881435242 +/- 0.0014862409190408148</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.007145085803432161 +/- 0.0009407059863763585</t>
+          <t>-0.009734789391575672 +/- 0.001736090825989835</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-0.004867394695787852 +/- 0.002364717044804577</t>
+          <t>-0.007519500780031219 +/- 0.0016943742879732295</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.0023712948517940593 +/- 0.0018416667161776884</t>
+          <t>0.027800312012480476 +/- 0.0025441934641991996</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.006552262090483596 +/- 0.0018927614212921368</t>
+          <t>-0.0003432137285491743 +/- 0.001837697887379353</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-0.001123244929797207 +/- 0.0019743266171053145</t>
+          <t>-0.0019656786271451065 +/- 0.001081293195080397</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-0.006677067082683341 +/- 0.0012019569600161125</t>
+          <t>0.004680187207488274 +/- 0.0019782673927173132</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.0036505460218408505 +/- 0.0008830559561987521</t>
+          <t>0.005397815912636506 +/- 0.0012716183383659806</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.005241809672386921 +/- 0.0012925001670644675</t>
+          <t>-0.009235569422776924 +/- 0.0017661119123974804</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>6.240249609981152e-05 +/- 0.00036386595287648193</t>
+          <t>0.00015600624024958432 +/- 0.0005079195193790979</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.00021840873634947354 +/- 0.001374626569230003</t>
+          <t>0.0024024960998439648 +/- 0.0009672386895475693</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-0.0017160686427457271 +/- 0.0013546516908637814</t>
+          <t>-0.013166926677067115 +/- 0.001060842433697341</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-0.0006552262090483762 +/- 0.001195866951434422</t>
+          <t>-0.00574102964118568 +/- 0.0018310640563021744</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.0005304212168486533 +/- 0.0012007414293225677</t>
+          <t>-0.00024960998439940154 +/- 0.002030719512670577</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.0006240249609984483 +/- 0.001765009126206665</t>
+          <t>-0.005085803432137326 +/- 0.001516072463432929</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.0004992199687987253 +/- 0.0004456429596594724</t>
+          <t>0.0014352574102963866 +/- 0.0006271373242509352</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.0005616224648985702 +/- 0.002160784985108372</t>
+          <t>0.001653666146645838 +/- 0.0016394764000523699</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-0.0034633385335413715 +/- 0.0013774564776688832</t>
+          <t>-0.008299531981279274 +/- 0.0013178603483271674</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-0.0027769110764430784 +/- 0.0014464058641496878</t>
+          <t>-0.011669266770670862 +/- 0.0016344213233957865</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.0009672386895475893 +/- 0.0013123083210491622</t>
+          <t>-0.01971918876755071 +/- 0.001140447231357067</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-0.0005304212168486866 +/- 0.0009969763063132978</t>
+          <t>-0.0012480499219969076 +/- 0.0004412522815516501</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.00046801872074885286 +/- 0.0005267376916110515</t>
+          <t>-0.00012480499219971186 +/- 0.00037441497659905233</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,122 +3716,122 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.0014352574102964421 +/- 0.0012417939932687797</t>
+          <t>-0.025273010920436833 +/- 0.0014092467757424187</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.005054602184087387 +/- 0.0013585985059018685</t>
+          <t>-0.007893915756630298 +/- 0.0017430861433339658</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>-0.0006240249609984705 +/- 0.0007893360774211217</t>
+          <t>-0.0015912636505460375 +/- 0.0007948667209271245</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.0007176287051482322 +/- 0.0005590163141082237</t>
+          <t>-0.000436817472698936 +/- 0.0006720954517484454</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.00012480499219967854 +/- 0.0018886422403022283</t>
+          <t>0.011014040561622451 +/- 0.001367526177897719</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>-0.003151326053042136 +/- 0.0015122147664340367</t>
+          <t>-0.0023088923556942587 +/- 0.0012650942235702472</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>0.0006240249609984261 +/- 0.0003417925475851519</t>
+          <t>-0.0008112324492979938 +/- 0.000672095451748431</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.002090483619344752 +/- 0.001125409597308644</t>
+          <t>0.0029017160686427455 +/- 0.0020839537571914497</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.0042121684867395095 +/- 0.001046521674336875</t>
+          <t>-0.012293291731669298 +/- 0.0020564439380073673</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-0.0022776911076443198 +/- 0.0014836185245514692</t>
+          <t>0.0005304212168486422 +/- 0.0018195972932072825</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-0.011232449297971948 +/- 0.001903020365925364</t>
+          <t>0.0009672386895475781 +/- 0.0013703707492042235</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>-0.004617784711388473 +/- 0.0018968716572319117</t>
+          <t>-0.010390015600624058 +/- 0.001686311278236706</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-0.00012480499219970077 +/- 0.0012650942235702517</t>
+          <t>0.0011544461778471016 +/- 0.0005590163141082528</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.0011544461778471237 +/- 0.0006401960851382937</t>
+          <t>-0.003619344773790978 +/- 0.0014647980772924197</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>0.0003744149765990357 +/- 0.00047932266757370765</t>
+          <t>0.0023712948517940593 +/- 0.0005258127783573223</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>-0.0019656786271451065 +/- 0.0009468949082991206</t>
+          <t>-0.00031201248049923526 +/- 0.001360030871619558</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>-0.010920436817472724 +/- 0.0015600624024960808</t>
+          <t>0.00012480499219967854 +/- 0.0012803921702766415</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-0.010670826833073322 +/- 0.0010139205497205655</t>
+          <t>0.010951638065522606 +/- 0.0024266869710266167</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.020031201248049933 +/- 0.0016732714730473524</t>
+          <t>0.0021528861154446076 +/- 0.0021771675537496987</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>0.0007488299531981157 +/- 0.00037441497659906713</t>
+          <t>-9.3603744149795e-05 +/- 0.0004423540367787271</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.00037441497659904675 +/- 0.0005719283238634595</t>
+          <t>-0.0004680187207488307 +/- 0.0011442821105080855</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>-0.00034321372854919654 +/- 9.360374414975059e-05</t>
+          <t>0.00040561622464897474 +/- 0.00024368953746979605</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-0.0177223088923557 +/- 0.002715763512884735</t>
+          <t>-0.009048361934477412 +/- 0.002305516780269722</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.011388455538221553 +/- 0.00157404034391631</t>
+          <t>-0.001154446177847146 +/- 0.0013314563677598614</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,92 +3841,92 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>0.0009048361934477112 +/- 0.0007310686124093721</t>
+          <t>0.00012480499219966746 +/- 0.0007004662814553533</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-0.003307332293291754 +/- 0.0009687472509366765</t>
+          <t>0.0019344773790951563 +/- 0.0016615946278557734</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.016318252730109218 +/- 0.0013093376136260441</t>
+          <t>6.240249609984483e-05 +/- 0.001690635530002388</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>-0.0003432137285491743 +/- 0.0005484678886504376</t>
+          <t>-9.3603744149795e-05 +/- 0.0006842967924949006</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-0.001123244929797229 +/- 0.0014243634584103913</t>
+          <t>-0.0033697347893916095 +/- 0.0014078644833295962</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.010514820592823737 +/- 0.0012168486739469525</t>
+          <t>-0.007550702028081136 +/- 0.0021426876397365752</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-0.0004056162246489969 +/- 0.0016215646128157652</t>
+          <t>-0.012574102964118605 +/- 0.0021255814452731453</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-1.1102230246251566e-17 +/- 0.0007514255587389988</t>
+          <t>0.005117004680187198 +/- 0.0012727661812400033</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>-0.00015600624024962871 +/- 0.0002876612935192797</t>
+          <t>0.00040561622464896363 +/- 0.0001997854676266256</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.002714508580343189 +/- 0.0010258522447908554</t>
+          <t>-0.0002496099843993793 +/- 0.0014284584264910765</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>-0.002808112324492984 +/- 0.0010808429376404963</t>
+          <t>-0.004243369734789404 +/- 0.0024136136793527457</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-0.0006552262090483874 +/- 0.000830797313927872</t>
+          <t>-0.0017472698907956441 +/- 0.001017753911407177</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.01207488299531977 +/- 0.0012168486739469499</t>
+          <t>0.008611544461778453 +/- 0.0018469452214600452</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-0.004586583463338567 +/- 0.001006693653972038</t>
+          <t>-0.003182527301092053 +/- 0.00137285491419655</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>0.004836193447737891 +/- 0.0010371775437500767</t>
+          <t>0.00854914196567862 +/- 0.0019644400921931034</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>-9.36037441497839e-05 +/- 0.0001429820809658882</t>
+          <t>-0.0005304212168486977 +/- 0.0003135686621254715</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0.0007800312012480437 +/- 0.0007149104048293198</t>
+          <t>0.0012168486739469243 +/- 0.0006611425928367306</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.0014664586583463368 +/- 0.0007257225179165759</t>
+          <t>0.0012792511700467912 +/- 0.0008189956161252237</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3936,52 +3936,52 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>0.0008736349453977943 +/- 0.00043681747269890903</t>
+          <t>-0.0005928237129485536 +/- 0.0005828874162954398</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>0.000624024960998415 +/- 0.0007250514844694169</t>
+          <t>-0.0057410296411856574 +/- 0.002263757522273584</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>6.240249609983373e-05 +/- 0.00012480499219966746</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>-0.00021840873634949577 +/- 0.0004197698610631566</t>
+          <t>0.000967238689547556 +/- 0.0004289462428975911</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>-0.0009048361934477667 +/- 0.0011628483715185114</t>
+          <t>-0.0069266770670827205 +/- 0.0016260610571975649</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.0019032761310452174 +/- 0.0013416536661466352</t>
+          <t>0.003494539781591255 +/- 0.001802125313971141</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>-0.0016224648985959545 +/- 0.0006208969966344057</t>
+          <t>-6.240249609985593e-05 +/- 0.0007488299531981416</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>-0.0031201248049922193 +/- 0.0012558260092042448</t>
+          <t>-0.006677067082683308 +/- 0.0012417939932687929</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>0.010733229329173144 +/- 0.0015860549175836292</t>
+          <t>0.00268330733229325 +/- 0.001249609010577259</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>-0.0013416536661466695 +/- 0.0012327454767637107</t>
+          <t>-0.00046801872074884174 +/- 0.0009792421108564715</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.008163866784556394 +/- 0.0017978190391983412</t>
+          <t>0.001679929266136193 +/- 0.0014259912058241131</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.005098732684939544 +/- 0.0018548917155979535</t>
+          <t>0.003949307397583301 +/- 0.0018788538108469577</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.01615089890951954 +/- 0.0012967875036840578</t>
+          <t>0.009195402298850608 +/- 0.0013034685757439468</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0069260241674034325 +/- 0.0014272089611321083</t>
+          <t>0.001827291482463933 +/- 0.0008419013767807606</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.009018567639257269 +/- 0.001714475634806837</t>
+          <t>0.003684055408193376 +/- 0.0017695741883027528</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.004361921603300967 +/- 0.00245454321410634</t>
+          <t>0.0027704096669614155 +/- 0.0027904038617258212</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.00023577954612433727 +/- 0.0002887697898948527</t>
+          <t>5.8944886531109296e-05 +/- 0.00011788977306221858</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.007102858826996706 +/- 0.0015508779389240017</t>
+          <t>0.0009725906277630702 +/- 0.0014620827297155891</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.033863837312113135 +/- 0.003213577691491844</t>
+          <t>0.03150604185086946 +/- 0.003202747505859711</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.03521956970232829 +/- 0.0030522126697919245</t>
+          <t>0.03262599469496025 +/- 0.0028454266472943703</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-0.0015915119363395735 +/- 0.002225901277748224</t>
+          <t>-0.008635425876805148 +/- 0.0018548917155979407</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.018773946360153206 +/- 0.0021008291644205083</t>
+          <t>0.002505157677571501 +/- 0.0010646856391505165</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0149130562923666 +/- 0.0011580832716998803</t>
+          <t>0.013203654582964953 +/- 0.0015302982594455972</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-0.005069260241674078 +/- 0.001971792358818485</t>
+          <t>-0.0005599764220453496 +/- 0.0020817227688075756</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.013586796345416995 +/- 0.0031231056878221345</t>
+          <t>0.019687592101385255 +/- 0.0013101155774178101</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.003890362511052137 +/- 0.0023199137818042245</t>
+          <t>0.004804008252284142 +/- 0.0017488362745825925</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.0034777483053344714 +/- 0.0014366115658065342</t>
+          <t>0.008340701444149745 +/- 0.0014441497200117814</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>-0.002151488358384934 +/- 0.001318377202849698</t>
+          <t>-0.0003241968759209901 +/- 0.0010824855686535268</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.0012967875036839938 +/- 0.0012656003863002628</t>
+          <t>-0.0004420866489831643 +/- 0.0014393298493457119</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.00023577954612434836 +/- 0.00022055157010159385</t>
+          <t>0.00032419687592106784 +/- 0.0002448165005280926</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.014412024756852392 +/- 0.002644156182417534</t>
+          <t>-0.008252284114353059 +/- 0.0016462410897458287</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>-0.01261420571765406 +/- 0.001513173905451627</t>
+          <t>-0.005128205128205099 +/- 0.0012656003863002524</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-0.001974653698791662 +/- 0.0013117720650909403</t>
+          <t>-0.0022399056881815317 +/- 0.0011803704329207772</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.0012378426171529068 +/- 0.0009577410438710289</t>
+          <t>0.0025346301208370448 +/- 0.0006348558570155597</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.004067197170645409 +/- 0.0012765345020753164</t>
+          <t>0.00943118184497498 +/- 0.0010209553831823613</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.00011788977306215198 +/- 0.000747926763362775</t>
+          <t>0.00020630710285888255 +/- 0.0004381393677370602</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.009637488947833738 +/- 0.002080053049053228</t>
+          <t>0.0011494252873563648 +/- 0.0024176387308948886</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-0.009283819628647261 +/- 0.002174778757957353</t>
+          <t>-0.01040377247273796 +/- 0.0023726689728946447</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>-0.0030651340996169173 +/- 0.0019691474315932877</t>
+          <t>-0.0005894488653109042 +/- 0.0015483555009211428</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.0005305039787798727 +/- 0.0013557323902151565</t>
+          <t>-0.0016209843796050395 +/- 0.0020000044299821503</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0010020630710285473 +/- 0.0006746550629094747</t>
+          <t>0.0006189213085765366 +/- 0.00046506731028764193</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.0002063071028587826 +/- 0.0006980677443163597</t>
+          <t>-0.0005010315355142625 +/- 0.00034996587347591463</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,122 +4161,122 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.0015915119363395624 +/- 0.0018272914824638796</t>
+          <t>-0.00247568523430588 +/- 0.001332467380543167</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.00842911877394641 +/- 0.0014269046197359545</t>
+          <t>-0.008281756557618591 +/- 0.0012325684448173542</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>-0.00038314176245215494 +/- 0.0002301871404629257</t>
+          <t>-0.00041261420571760967 +/- 0.00019549807193368956</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.0025641025641026218 +/- 0.00047614189276168215</t>
+          <t>-0.0010020630710285473 +/- 0.0007243268922749415</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.0019451812555260407 +/- 0.0016940887548717667</t>
+          <t>0.00433244916003539 +/- 0.0014973045441650972</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>-0.008458591217211953 +/- 0.0011109977497772343</t>
+          <t>-0.005865016209843754 +/- 0.0013275691870975647</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-0.001208370173887463 +/- 0.0008382825024066006</t>
+          <t>-0.0003831417624520661 +/- 0.000884664368983416</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.005010315355142891 +/- 0.0010868900038070017</t>
+          <t>0.0013262599469496372 +/- 0.0006355396007323247</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.012761567933981777 +/- 0.0012917540230362966</t>
+          <t>-0.0004420866489831643 +/- 0.0011357411652223814</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-0.0013852048334807355 +/- 0.002483567091987292</t>
+          <t>0.0053934571175950794 +/- 0.001473916858243439</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-0.013262599469496062 +/- 0.0028967078986868533</t>
+          <t>-0.0056587091069849275 +/- 0.0010772571106688565</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.00751547303271437 +/- 0.0019337606486677364</t>
+          <t>0.013144709696433865 +/- 0.0029946090883302243</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-0.0038314176245211164 +/- 0.0008643016975310982</t>
+          <t>0.0011494252873563426 +/- 0.0012112421213106275</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.0022988505747127074 +/- 0.0011322942948599245</t>
+          <t>-0.007898614795166481 +/- 0.0015584207564282256</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-0.0017978190391983895 +/- 0.0005010315355142919</t>
+          <t>-0.0006189213085764589 +/- 0.0009990245362026724</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>0.0040082522841143 +/- 0.001841497123703319</t>
+          <t>0.003978779840848845 +/- 0.0010230801625528856</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.00014736221632769553 +/- 0.0013522039194759235</t>
+          <t>0.007869142351901014 +/- 0.001305133499881186</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0038903625110521143 +/- 0.0017073679172366911</t>
+          <t>-0.0008547008547008072 +/- 0.0018426759837713697</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.000943118184497449 +/- 0.0019136673245797881</t>
+          <t>0.0019157088122605747 +/- 0.002118123620257103</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-0.0007073386383731784 +/- 0.0007479267633627768</t>
+          <t>0.00047155909224878557 +/- 0.0003774314316199692</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.001002063071028536 +/- 0.0005138696072550117</t>
+          <t>-0.0005010315355142625 +/- 0.0003739633816814063</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>-0.0002947244326555132 +/- 0.0002636095464190823</t>
+          <t>-8.841732979664174e-05 +/- 0.0002652519893899252</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-0.006601827291482521 +/- 0.0017545388819495676</t>
+          <t>0.0012378426171529733 +/- 0.001602390476754279</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.0005010315355142514 +/- 0.001407598459918592</t>
+          <t>-0.007073386383731184 +/- 0.0006040053501891895</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4286,147 +4286,147 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-0.0008252284114353637 +/- 0.0007314868049508315</t>
+          <t>-0.0009136457412319277 +/- 0.0009902916366879755</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-0.004627173592690892 +/- 0.0007803243321469925</t>
+          <t>-0.004568228706159716 +/- 0.0008151675028552676</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-0.0035661656351312133 +/- 0.001695370117096322</t>
+          <t>-0.005629236663719395 +/- 0.0015620394930739834</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>-0.00026525198938994745 +/- 0.0005010315355142893</t>
+          <t>0.00023577954612441498 +/- 0.0006694852161273653</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-0.0049808429118774365 +/- 0.001516900587380813</t>
+          <t>-0.004420866489831965 +/- 0.002020528912585057</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-0.0005010315355143402 +/- 0.002260173247278266</t>
+          <t>0.0050103153551429806 +/- 0.0016409561929944059</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-0.0013852048334807466 +/- 0.0014856567239762543</t>
+          <t>0.0011788977306219084 +/- 0.0012573374009844655</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-0.008075449454759843 +/- 0.0010884871979144708</t>
+          <t>-0.0013262599469495706 +/- 0.0014211097496305578</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>-0.0006778661951076348 +/- 0.0002961943890692922</t>
+          <t>0.000383141762452166 +/- 0.00023018714046290723</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.00023577954612431508 +/- 0.0012137495008531576</t>
+          <t>-0.004627173592690803 +/- 0.0015486359747031732</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>-0.0022104332449160435 +/- 0.0011807383214860212</t>
+          <t>0.0018862363689950313 +/- 0.0009880963521508984</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-0.00020630710285888255 +/- 0.0008547008547008321</t>
+          <t>-0.001915708812260497 +/- 0.0005782910955009757</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.011405835543766518 +/- 0.002462492743330892</t>
+          <t>0.005481874447391721 +/- 0.001509725726479873</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>-0.000795755968169809 +/- 0.0013314891833865708</t>
+          <t>-0.0014146772767462345 +/- 0.0016185712016205157</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>0.00017683465959322797 +/- 0.0017693287379668373</t>
+          <t>-0.0040082522841143105 +/- 0.0011121698947311068</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>5.894488653106489e-05 +/- 0.00022055157010162943</t>
+          <t>-0.00011788977306215198 +/- 0.00027011940435932346</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0.00023577954612432616 +/- 0.000556084947365526</t>
+          <t>0.000648393751842069 +/- 0.00047155909224873147</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>-0.003300913645741277 +/- 0.0005239136113949516</t>
+          <t>-0.0003536693191865337 +/- 0.000766283524904234</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00011788977306221859 +/- 0.00014438489494747052</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>-0.0025051576775715345 +/- 0.0006880411158225235</t>
+          <t>0.0007073386383731562 +/- 0.0009150707159599242</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-0.00447981137636313 +/- 0.0011700225901137137</t>
+          <t>0.003006189213085808 +/- 0.0013621243746880533</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>-8.841732979665284e-05 +/- 0.00018871571581000805</t>
+          <t>-2.9472443265543545e-05 +/- 8.841732979663064e-05</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.00035366931918652257 +/- 0.0007548628632399436</t>
+          <t>-0.0022988505747125964 +/- 0.0010691634039031693</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>-0.0023283230179782398 +/- 0.0010162652313331234</t>
+          <t>-0.0015915119363394958 +/- 0.0011043320952075055</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0.0006483937518419914 +/- 0.0007662835249042108</t>
+          <t>-0.002740937223695805 +/- 0.0014739168582434449</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>-0.0015030946065429207 +/- 0.0007273187550399677</t>
+          <t>-0.0008841732979663508 +/- 0.0008643016975311096</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>0.0023577954612436836 +/- 0.001748587913255689</t>
+          <t>0.008812260536398508 +/- 0.0012535319963534648</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>-0.001974653698791662 +/- 0.0015709116382241664</t>
+          <t>-0.0018272914824638664 +/- 0.0016817380038534795</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>-0.002033598585322782 +/- 0.0008587563975439642</t>
+          <t>0.00020630710285884923 +/- 0.0006727210262607244</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.0051570152693747985 +/- 0.000849288560817275</t>
+          <t>-0.008297320656871254 +/- 0.0016439461385983351</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.011264765197349435 +/- 0.0013963262248404087</t>
+          <t>-0.012561221549985634 +/- 0.00118926922734374</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.010717372515125289 +/- 0.0016936834867990749</t>
+          <t>-0.008470181503889406 +/- 0.0017486592803795382</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.007231345433592662 +/- 0.0019516611413932423</t>
+          <t>0.0021895707288965395 +/- 0.002013414602092337</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.010025929127052701 +/- 0.002011764938069268</t>
+          <t>-0.004840103716508249 +/- 0.0011437299476392579</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.002967444540478237 +/- 0.0010936475307463055</t>
+          <t>-0.000605012964563556 +/- 0.0013963262248404104</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0004321521175454257 +/- 0.00026561637733484424</t>
+          <t>2.881014116966618e-05 +/- 0.0002717943282067651</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.0008066839527513303 +/- 0.0012676462114664378</t>
+          <t>-0.0014116969173149196 +/- 0.0010814361497622313</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.0024200518582541243 +/- 0.0025450951109602664</t>
+          <t>-0.008758282915586335 +/- 0.0024350961232054817</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.001757418611351158 +/- 0.002306431294684574</t>
+          <t>-0.005733218092768677 +/- 0.002516397202916465</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-0.013915298184961077 +/- 0.0015624024042588621</t>
+          <t>-0.014116969173148985 +/- 0.0009641717390194007</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.006367041198501844 +/- 0.0014199045266898986</t>
+          <t>-0.01734370498415445 +/- 0.0014959095345142143</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.008153269951022734 +/- 0.002312182106278698</t>
+          <t>-0.005906078939786852 +/- 0.0014476916769116787</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>-0.00962258715067702 +/- 0.002512270741180267</t>
+          <t>-0.0062806107749928345 +/- 0.0028104289019319387</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.006424661480841276 +/- 0.0023513382198491234</t>
+          <t>0.011495246326706987 +/- 0.0033061441499745857</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.0016133679055027605 +/- 0.0014531282296650634</t>
+          <t>0.005675597810429212 +/- 0.0012495101378393186</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.003428406799193284 +/- 0.0015485283376982543</t>
+          <t>-0.0036876980697205576 +/- 0.0015610737175619732</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.002276001152405671 +/- 0.0011628024241204632</t>
+          <t>0.000576202823393801 +/- 0.0014633736789628692</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.003543647363872049 +/- 0.001123595505617986</t>
+          <t>-0.002967444540478281 +/- 0.0017762100422700567</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.0006914433880726434 +/- 0.0003457216940362847</t>
+          <t>0.00023048112935751818 +/- 0.00028228058113317315</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.005041774704696089 +/- 0.0014476916769116854</t>
+          <t>-0.000749063670411998 +/- 0.0022619171911714663</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.001123595505617947 +/- 0.0014828129337318024</t>
+          <t>0.002996254681647925 +/- 0.000991336821324421</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.0031403053874964337 +/- 0.0008590061374748236</t>
+          <t>0.001065975223278559 +/- 0.0008837719187656712</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.0020167098818784424 +/- 0.0009980125655827483</t>
+          <t>0.0009219245174301172 +/- 0.0010841191427385175</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.002765773552290429 +/- 0.0012168661528056779</t>
+          <t>0.0008066839527513415 +/- 0.0012411788665248175</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.002938634399308593 +/- 0.000460962258715085</t>
+          <t>0.0007778738115816642 +/- 0.0005161761125660969</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.004177470469605338 +/- 0.0009401998773886984</t>
+          <t>0.001267646211466411 +/- 0.001289716467046916</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-0.004840103716508182 +/- 0.002131950446557201</t>
+          <t>0.007634687409968266 +/- 0.001441946846008891</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>-0.004696053010659717 +/- 0.0011382740573401453</t>
+          <t>0.0036012676462114255 +/- 0.0015740464856983667</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.01950446557188127 +/- 0.002534801293411012</t>
+          <t>-0.01604724863151833 +/- 0.0018894269584638045</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>-0.0016421780466724157 +/- 0.0005473926822241249</t>
+          <t>8.643042350904295e-05 +/- 0.0005473926822241413</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.001037165082108904 +/- 0.0004311907100862836</t>
+          <t>0.0009219245174300949 +/- 0.0007150488992216003</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,122 +4606,122 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.01682512244309995 +/- 0.002687848755906807</t>
+          <t>-0.00861423220973786 +/- 0.0027406001706623967</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.001469317199654241 +/- 0.0026039331729756855</t>
+          <t>0.003428406799193284 +/- 0.001652255944562336</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>-0.0008643042350907293 +/- 0.0003865286045807726</t>
+          <t>-0.0023048112935753705 +/- 0.001022658562333555</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-0.0004033419763756596 +/- 0.0008066839527513549</t>
+          <t>0.0016421780466724268 +/- 0.0006185799640905718</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.007260155574762339 +/- 0.0017562374709453351</t>
+          <t>0.002708153269950997 +/- 0.0011610165185600477</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>-0.001065975223278548 +/- 0.0017431921068747672</t>
+          <t>0.004148660328435594 +/- 0.0014531282296650447</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>0.0013252664938058433 +/- 0.0006842029436495645</t>
+          <t>0.0012964563526360994 +/- 0.0011826203256568063</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.007087294727744197 +/- 0.0014531282296650525</t>
+          <t>0.0038605589167386655 +/- 0.001376871581140704</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.0007202535292422652 +/- 0.001800345698642231</t>
+          <t>-0.008815903197925712 +/- 0.0014925766461525464</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.002477672140593512 +/- 0.0012961362004266128</t>
+          <t>-0.004033419763756862 +/- 0.0012086532390321353</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-0.02085854220685679 +/- 0.0011822693476625287</t>
+          <t>-0.014635551714203443 +/- 0.0013623267551180396</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>-0.0014405070584845637 +/- 0.0012290826279286427</t>
+          <t>0.0017286084701814807 +/- 0.0011948396054927998</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0011812157879573792 +/- 0.0008781187354726639</t>
+          <t>-0.0035148372227024162 +/- 0.0009450428963904693</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.004984154422356657 +/- 0.0012627258427433685</t>
+          <t>-0.0006050129645635671 +/- 0.0008590061374748214</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.0007778738115817085 +/- 0.0005161761125660858</t>
+          <t>-0.0002016709881878742 +/- 0.0006576036998278964</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>-0.0017862287525208353 +/- 0.0010210340044177013</t>
+          <t>-0.0014693171996543076 +/- 0.0012784043637184674</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>-0.025180063382310547 +/- 0.0012832646183416952</t>
+          <t>-0.018985883030826857 +/- 0.001437334449238408</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-0.029472774416594606 +/- 0.0011382740573401434</t>
+          <t>-0.01696917314894846 +/- 0.0012185702093089582</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-0.035955056179775256 +/- 0.0015069659268939202</t>
+          <t>-0.01063094209161628 +/- 0.0011769921184566806</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>0.0007778738115816975 +/- 0.0006823808287137294</t>
+          <t>0.0009219245174301172 +/- 0.0004425897866821316</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.002247191011235994 +/- 0.0005435886564135219</t>
+          <t>0.0005185825410544131 +/- 0.0007815995370930885</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>-2.8810141169643978e-05 +/- 0.00030078670437657626</t>
+          <t>-0.00017286084701817472 +/- 0.0003689498264150359</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-0.017113223854796866 +/- 0.0018724375464444871</t>
+          <t>-0.024402189570728917 +/- 0.0017288485380210453</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.026332469029098214 +/- 0.0009744473941393165</t>
+          <t>-0.009997118985883059 +/- 0.0014749554291178574</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4731,107 +4731,107 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>0.002189570728896595 +/- 0.0009308841498935963</t>
+          <t>0.0006626332469028773 +/- 0.0006050129645635238</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-0.009305675597810415 +/- 0.0015410059487544093</t>
+          <t>-0.0049553442811869795 +/- 0.0005876138880544952</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-0.011696917314894816 +/- 0.0015146573815148269</t>
+          <t>-0.009075194468452919 +/- 0.0012374953382261425</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>-0.00043215211754535907 +/- 0.001016553083513532</t>
+          <t>-0.000547392682224157 +/- 0.0006750431872002349</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-0.007288965715931994 +/- 0.0017479471405494103</t>
+          <t>-0.00034572169403631616 +/- 0.0017750414060212511</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-0.03607029674445402 +/- 0.0012003841346009511</t>
+          <t>-0.015413425525785096 +/- 0.0009748731959486324</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-0.0004321521175453369 +/- 0.001823251781307599</t>
+          <t>0.007260155574762306 +/- 0.00227143801145803</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>0.00864304235090756 +/- 0.0014970188483741347</t>
+          <t>0.009017574186113486 +/- 0.0015517410555453985</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>0.0027945836934601285 +/- 0.0004282935392485955</t>
+          <t>0.0013540766349754985 +/- 0.0003169115528666116</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.00884471333909539 +/- 0.0014522711796172308</t>
+          <t>0.009997118985883003 +/- 0.0014058050012971416</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.004782483434168849 +/- 0.0010871773128270149</t>
+          <t>0.006222990492653379 +/- 0.0013647616574274724</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-0.0008931143762604177 +/- 0.0009331106160012462</t>
+          <t>0.0008354940939210409 +/- 0.0010343603037174438</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.01371362719677328 +/- 0.001594739556680846</t>
+          <t>0.016047248631518275 +/- 0.000835494093921062</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>0.002679343128781364 +/- 0.0009295457104524309</t>
+          <t>0.004782483434168805 +/- 0.0012438509446800867</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>0.007836358398156185 +/- 0.001374458132166699</t>
+          <t>0.009593777009507299 +/- 0.0020455200230481228</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>-2.8810141169655078e-05 +/- 0.00027179432820676624</t>
+          <t>0.00023048112935749598 +/- 0.0002822805811331686</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.0034860270815327277 +/- 0.0010263044154743258</t>
+          <t>0.0026793431287812975 +/- 0.0011882218742322922</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>0.0005762028233938677 +/- 0.001062465509339407</t>
+          <t>-0.0005762028233938565 +/- 0.0006938400794463992</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>0.00011524056467879796 +/- 0.00014114029056662848</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>0.006799193316047281 +/- 0.0012236681406854167</t>
+          <t>0.0021319504465571737 +/- 0.0006842029436495422</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>0.003255545952175187 +/- 0.0009384325828235289</t>
+          <t>0.0019878997407086984 +/- 0.0013540766349755214</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -4841,37 +4841,37 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.0016133679055027716 +/- 0.0011822693476625378</t>
+          <t>-0.0005762028233938565 +/- 0.0008046234539768888</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.001699798329011848 +/- 0.0014373344492384283</t>
+          <t>0.009276865456640693 +/- 0.0018028796136170511</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.008556611927398483 +/- 0.0017574186113511752</t>
+          <t>0.007634687409968266 +/- 0.0017864610772604273</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>0.00164217804667246 +/- 0.001195186892117037</t>
+          <t>-0.0016709881878421596 +/- 0.0014565513868930505</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>-0.0024200518582540797 +/- 0.0010323522251321857</t>
+          <t>-0.00227600115240566 +/- 0.0012388360702967412</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>0.002621722846441965 +/- 0.0018150388936905622</t>
+          <t>0.0033419763756842302 +/- 0.0014870052319866302</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>0.0022183808700662945 +/- 0.001249510137839333</t>
+          <t>0.0031114952463266675 +/- 0.0010046439512626224</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.005353955978584168 +/- 0.001356544229743174</t>
+          <t>-0.006722189173111248 +/- 0.001714876300463956</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.005294467578822126 +/- 0.0012464203949885217</t>
+          <t>-0.007555026769779894 +/- 0.0013248695687876344</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5.948839976206432e-05 +/- 0.0009573751897341394</t>
+          <t>0.002260559190957745 +/- 0.0012910490430821356</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.001725163593099377 +/- 0.0009480890809344967</t>
+          <t>0.002914931588340275 +/- 0.0023676084166725066</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0006246281975014866 +/- 0.0010843382589862157</t>
+          <t>-0.004015466983938132 +/- 0.001452601480913114</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.007436049970255809 +/- 0.0016399820050077667</t>
+          <t>0.007198096371207607 +/- 0.0022683731070717045</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.9744199881021062e-05 +/- 0.00016017741841564892</t>
+          <t>-0.0005353955978584124 +/- 0.00029143245006345563</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.00044616299821533814 +/- 0.0014707597043517068</t>
+          <t>0.0021415823914336606 +/- 0.001455947442060717</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.023735871505056537 +/- 0.00267300915391566</t>
+          <t>0.022516359309934585 +/- 0.002412949519614177</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.028524687685901252 +/- 0.002366300190743455</t>
+          <t>0.02798929208804283 +/- 0.002717812685666234</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-0.000832837596668623 +/- 0.0006210771272403882</t>
+          <t>8.923259964305208e-05 +/- 0.0011053482555658497</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.0017846519928613747 +/- 0.001282799443952888</t>
+          <t>-0.0013682331945270687 +/- 0.001969416461302428</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.0016954193932183336 +/- 0.0013503342608942443</t>
+          <t>0.006246281975014867 +/- 0.0012689309344260206</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.01796549672813803 +/- 0.001291049043082122</t>
+          <t>0.02227840571088635 +/- 0.0017967564914383016</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.02150505651397979 +/- 0.0022180878271864444</t>
+          <t>0.032897085068411644 +/- 0.0024317588858976356</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>-0.0006246281975014756 +/- 0.0009725034339245817</t>
+          <t>-0.0024687685901249256 +/- 0.0011053482555658431</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.0028256989886972007 +/- 0.0010989264248608655</t>
+          <t>-0.0013384889946460587 +/- 0.0013252034152257852</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.0024390243902439046 +/- 0.0012321424852592296</t>
+          <t>0.0016656751933372903 +/- 0.0013836648839515733</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-0.006038072575847686 +/- 0.0011600237953599067</t>
+          <t>-0.004342653182629386 +/- 0.000933039092287806</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00020820939916715853 +/- 0.00026769779892921793</t>
+          <t>0.00026769779892920064 +/- 0.0003630742300932025</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.00118976799524092 +/- 0.001096911892598784</t>
+          <t>-0.00324211778703154 +/- 0.0009354066147243649</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-0.002022605591909554 +/- 0.0008803479230784586</t>
+          <t>0.00011897679952408425 +/- 0.001318174884364087</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.0011302795954788892 +/- 0.0006351622993474841</t>
+          <t>0.004372397382510385 +/- 0.0009596826772695848</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.002439024390243916 +/- 0.000817830284644116</t>
+          <t>0.0032421177870315177 +/- 0.000896776527762124</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.0015764425936942382 +/- 0.001121241928909615</t>
+          <t>0.0024687685901249256 +/- 0.0017447958805547191</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.0008923259964306763 +/- 0.0004206465087368011</t>
+          <t>-0.0014872099940511751 +/- 0.0004411777803150212</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.0056216537775134025 +/- 0.0013659681740874595</t>
+          <t>0.00541344437834621 +/- 0.0021564032076611386</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0.004997025580011916 +/- 0.0013355112623821348</t>
+          <t>0.0070791195716835235 +/- 0.0020812439838829053</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>-0.0002379535990481685 +/- 0.0005919021041681225</t>
+          <t>0.0020226055919095654 +/- 0.0011808110197072785</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.00011897679952407313 +/- 0.0010060401264299823</t>
+          <t>0.00023795359904815738 +/- 0.0013617517123449907</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-0.0003866745984532738 +/- 0.0002989255092540204</t>
+          <t>0.0011897679952409313 +/- 0.0006239196003391556</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.0012790005948839834 +/- 0.00042169681376436925</t>
+          <t>0.0003271861986912317 +/- 0.00020820939916714744</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,122 +5051,122 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.0014277215942891108 +/- 0.00108719017742399</t>
+          <t>-0.0016656751933373016 +/- 0.0011145148123257026</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.006157049375371826 +/- 0.002078053358085489</t>
+          <t>0.00562165377751338 +/- 0.00198841700337399</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>-0.001933372992266491 +/- 0.00042587213156680475</t>
+          <t>-0.003331350386674614 +/- 0.0007013578895033606</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.0007138607971445387 +/- 0.000501258166161594</t>
+          <t>0.0008923259964306873 +/- 0.000479610811915447</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.0034800713860797194 +/- 0.001255261620821491</t>
+          <t>0.002647233789411052 +/- 0.001042745279176558</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>-0.0004461629982153159 +/- 0.0008008870920783106</t>
+          <t>-0.006692444973230227 +/- 0.0016359309934562694</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-0.0006543723973824967 +/- 0.00045693906887976404</t>
+          <t>-0.0005651397977394446 +/- 0.0006302682956697516</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.0038964901844140477 +/- 0.0008460120555221898</t>
+          <t>0.009726353361094564 +/- 0.0017243941749715236</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.001516954193932163 +/- 0.0008868561282495846</t>
+          <t>-0.0016359309934562804 +/- 0.0009706822648471576</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.001041046995835826 +/- 0.0012281869614552427</t>
+          <t>0.002260559190957756 +/- 0.0012703245986949582</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-0.010023795359904797 +/- 0.0011975503949552498</t>
+          <t>-0.009845330160618693 +/- 0.0014354465808463657</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.0014872099940511751 +/- 0.0011823085612344922</t>
+          <t>0.003926234384295057 +/- 0.0021970476279142832</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.003182629387269498 +/- 0.001004720151936606</t>
+          <t>-0.0016954193932183447 +/- 0.0010478236141468712</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.004104699583581217 +/- 0.0012030784304673872</t>
+          <t>-0.0016359309934562804 +/- 0.0013117832879952428</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-0.0005056513979773581 +/- 0.0006102999562368582</t>
+          <t>-0.0008923259964307096 +/- 0.0002303975815709614</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>-0.002349791790600819 +/- 0.0012296268059842192</t>
+          <t>0.0071683521713265756 +/- 0.0010678954831062689</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.0116597263533611 +/- 0.001633495564276731</t>
+          <t>0.0001487209994051053 +/- 0.0019515912792771233</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-0.004342653182629363 +/- 0.002035685738520954</t>
+          <t>-0.007495538370017829 +/- 0.001584000827566258</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-0.01567519333729921 +/- 0.002013179209877182</t>
+          <t>-0.012433075550267703 +/- 0.00225271817117924</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-0.000535395597858379 +/- 0.0002225852103970061</t>
+          <t>-0.0010113027959548048 +/- 0.00030333251121909165</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>-0.0002676977989291895 +/- 0.0003866745984532738</t>
+          <t>0.00032718619869124275 +/- 0.0004693555573485808</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.00011897679952408425 +/- 0.00014571622503170743</t>
+          <t>-0.0008923259964306984 +/- 0.0004607951631418798</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-0.0024092801903628724 +/- 0.0011781857418404602</t>
+          <t>-0.0077037477691850095 +/- 0.0012510256302684683</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-0.001933372992266491 +/- 0.001646711544993042</t>
+          <t>-0.002201070791195725 +/- 0.0011065481997464808</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,92 +5176,92 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>0.00017846519928615967 +/- 0.00038091161436246287</t>
+          <t>-0.001397977394408101 +/- 0.000652341231393871</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-0.0036882807852468558 +/- 0.0007430098748838122</t>
+          <t>0.0012195121951219412 +/- 0.0009448173809796862</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>0.0005056513979774024 +/- 0.0007412216415453289</t>
+          <t>-0.002974419988102328 +/- 0.0016930695384601822</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.00020820939916718073 +/- 0.0005160425809904137</t>
+          <t>-0.0015466983938131952 +/- 0.00043714867509514645</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.0008923259964307096 +/- 0.0013235333409450912</t>
+          <t>0.0038964901844140364 +/- 0.0009162951695865186</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-0.01308744794765021 +/- 0.0014449682095765588</t>
+          <t>-0.005651397977394413 +/- 0.0016825860349471572</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>0.010469958358120179 +/- 0.0016442920834128642</t>
+          <t>-0.0006543723973825077 +/- 0.0016972448087670645</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-0.002022605591909554 +/- 0.0008391871492960187</t>
+          <t>-0.00020820939916715853 +/- 0.0011053482555658464</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>-0.0002379535990481685 +/- 0.00025930392287569064</t>
+          <t>-0.0008923259964306984 +/- 0.00042064650873680897</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.0019928613920285666 +/- 0.0012900207282689655</t>
+          <t>0.0005948839976204434 +/- 0.0013951266388528979</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.0006246281975014866 +/- 0.001034225975652189</t>
+          <t>-0.0011600237953599101 +/- 0.0008768234963107634</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-0.0013384889946460254 +/- 0.0009887430183578134</t>
+          <t>-0.002468768590124937 +/- 0.0006789239863482238</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-0.000803093396787602 +/- 0.0014391398457350361</t>
+          <t>-0.0023200475907198203 +/- 0.0013938577648852063</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-0.0003271861986912317 +/- 0.0014042916875803614</t>
+          <t>-0.0012790005948839945 +/- 0.0011446687331882074</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>0.0013087447947650378 +/- 0.001910124254372673</t>
+          <t>-0.0016359309934562804 +/- 0.0012706727759246705</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>-8.923259964306318e-05 +/- 0.0001904558071812132</t>
+          <t>-0.00023795359904817958 +/- 0.0003203548368313205</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>-0.001160023795359877 +/- 0.000745980737893183</t>
+          <t>0.00047590719809635916 +/- 0.0005674831656258077</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8.923259964309649e-05 +/- 0.000400167282780314</t>
+          <t>-0.000743604997025582 +/- 0.0005524739922964569</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5271,52 +5271,52 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>-0.00017846519928611527 +/- 0.000667755631191046</t>
+          <t>0.0002974419988102217 +/- 0.0004977156612338185</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>-0.005353955978584168 +/- 0.0013695258100203688</t>
+          <t>-0.005026769779892926 +/- 0.0013852624654604364</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0003271861986912317 +/- 0.00016017741841564892</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>-0.00047590719809634805 +/- 0.000464619254961712</t>
+          <t>0.000743604997025582 +/- 0.000583623345340535</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>-0.0014574657941701207 +/- 0.0012078489294614515</t>
+          <t>-0.002230814991076746 +/- 0.0006943853378898723</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>-0.005978584176085644 +/- 0.0014354465808463378</t>
+          <t>0.0022605591909577337 +/- 0.0015466983938132014</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>-0.0005948839976204767 +/- 0.0007641423306760901</t>
+          <t>-0.0030933967876264233 +/- 0.0009424734989741186</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>-0.004045211183819142 +/- 0.0010490893568440545</t>
+          <t>-0.0042831647828673325 +/- 0.0009972072941249299</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>0.0009220701963117306 +/- 0.0017619516025722361</t>
+          <t>-0.0022903033908387993 +/- 0.0012762306932138474</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>-0.001100535395597857 +/- 0.0013698487733098798</t>
+          <t>0.0013682331945270576 +/- 0.0008641189200674528</t>
         </is>
       </c>
     </row>
